--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_retail_special_lines.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cose_odel_n0000" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0518</v>
+        <v>0.0509</v>
       </c>
       <c r="G2">
-        <v>-0.04423076923076923</v>
+        <v>0.1091633466135458</v>
       </c>
       <c r="H2">
-        <v>-0.04423076923076923</v>
+        <v>0.1091633466135458</v>
       </c>
       <c r="I2">
-        <v>-0.1592307692307692</v>
+        <v>0.100398406374502</v>
       </c>
       <c r="J2">
-        <v>-0.1592307692307692</v>
+        <v>0.100398406374502</v>
       </c>
       <c r="K2">
-        <v>-7.55</v>
+        <v>-4.15</v>
       </c>
       <c r="L2">
-        <v>-0.2903846153846154</v>
+        <v>-0.1653386454183267</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.592</v>
+        <v>0.212</v>
       </c>
       <c r="V2">
-        <v>0.01751479289940829</v>
+        <v>0.0165625</v>
       </c>
       <c r="W2">
-        <v>-0.2194767441860465</v>
+        <v>-0.154275092936803</v>
       </c>
       <c r="X2">
-        <v>0.4289849227685005</v>
+        <v>1.087823778233142</v>
       </c>
       <c r="Y2">
-        <v>-0.6484616669545471</v>
+        <v>-1.242098871169945</v>
       </c>
       <c r="Z2">
-        <v>0.2497526488189582</v>
+        <v>0.2265792846955172</v>
       </c>
       <c r="AA2">
-        <v>-0.03976830638886487</v>
+        <v>0.02274819910090451</v>
       </c>
       <c r="AB2">
-        <v>0.1749863568654615</v>
+        <v>0.3371179051693061</v>
       </c>
       <c r="AC2">
-        <v>-0.2147546632543264</v>
+        <v>-0.3143697060684016</v>
       </c>
       <c r="AD2">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="AG2">
-        <v>86.108</v>
+        <v>52.08799999999999</v>
       </c>
       <c r="AH2">
-        <v>0.7195020746887967</v>
+        <v>0.8033794162826421</v>
       </c>
       <c r="AI2">
-        <v>0.7632042253521127</v>
+        <v>0.8083462132921174</v>
       </c>
       <c r="AJ2">
-        <v>0.7181172232044568</v>
+        <v>0.8027370237948466</v>
       </c>
       <c r="AK2">
-        <v>0.7619637547784227</v>
+        <v>0.8077161642476118</v>
       </c>
       <c r="AL2">
-        <v>5.39</v>
+        <v>5.81</v>
       </c>
       <c r="AM2">
-        <v>5.367999999999999</v>
+        <v>5.81</v>
       </c>
       <c r="AN2">
-        <v>-893.8144329896908</v>
+        <v>11.15138592750533</v>
       </c>
       <c r="AO2">
-        <v>-0.7680890538033395</v>
+        <v>0.4337349397590362</v>
       </c>
       <c r="AP2">
-        <v>-887.7113402061856</v>
+        <v>11.10618336886993</v>
       </c>
       <c r="AQ2">
-        <v>-0.7712369597615499</v>
+        <v>0.4337349397590362</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0518</v>
+        <v>0.0509</v>
       </c>
       <c r="G3">
-        <v>-0.04423076923076923</v>
+        <v>0.1091633466135458</v>
       </c>
       <c r="H3">
-        <v>-0.04423076923076923</v>
+        <v>0.1091633466135458</v>
       </c>
       <c r="I3">
-        <v>-0.1592307692307692</v>
+        <v>0.100398406374502</v>
       </c>
       <c r="J3">
-        <v>-0.1592307692307692</v>
+        <v>0.100398406374502</v>
       </c>
       <c r="K3">
-        <v>-7.55</v>
+        <v>-4.15</v>
       </c>
       <c r="L3">
-        <v>-0.2903846153846154</v>
+        <v>-0.1653386454183267</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.592</v>
+        <v>0.212</v>
       </c>
       <c r="V3">
-        <v>0.01751479289940829</v>
+        <v>0.0165625</v>
       </c>
       <c r="W3">
-        <v>-0.2194767441860465</v>
+        <v>-0.154275092936803</v>
       </c>
       <c r="X3">
-        <v>0.4289849227685005</v>
+        <v>1.087823778233142</v>
       </c>
       <c r="Y3">
-        <v>-0.6484616669545471</v>
+        <v>-1.242098871169945</v>
       </c>
       <c r="Z3">
-        <v>0.2497526488189582</v>
+        <v>0.2265792846955172</v>
       </c>
       <c r="AA3">
-        <v>-0.03976830638886487</v>
+        <v>0.02274819910090451</v>
       </c>
       <c r="AB3">
-        <v>0.1749863568654615</v>
+        <v>0.3371179051693061</v>
       </c>
       <c r="AC3">
-        <v>-0.2147546632543264</v>
+        <v>-0.3143697060684016</v>
       </c>
       <c r="AD3">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="AG3">
-        <v>86.108</v>
+        <v>52.08799999999999</v>
       </c>
       <c r="AH3">
-        <v>0.7195020746887967</v>
+        <v>0.8033794162826421</v>
       </c>
       <c r="AI3">
-        <v>0.7632042253521127</v>
+        <v>0.8083462132921174</v>
       </c>
       <c r="AJ3">
-        <v>0.7181172232044568</v>
+        <v>0.8027370237948466</v>
       </c>
       <c r="AK3">
-        <v>0.7619637547784227</v>
+        <v>0.8077161642476118</v>
       </c>
       <c r="AL3">
-        <v>5.39</v>
+        <v>5.81</v>
       </c>
       <c r="AM3">
-        <v>5.367999999999999</v>
+        <v>5.81</v>
       </c>
       <c r="AN3">
-        <v>-893.8144329896908</v>
+        <v>11.15138592750533</v>
       </c>
       <c r="AO3">
-        <v>-0.7680890538033395</v>
+        <v>0.4337349397590362</v>
       </c>
       <c r="AP3">
-        <v>-887.7113402061856</v>
+        <v>11.10618336886993</v>
       </c>
       <c r="AQ3">
-        <v>-0.7712369597615499</v>
+        <v>0.4337349397590362</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Odel PLC (COSE:ODEL.N0000)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COSE:ODEL.N0000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Retail (Special Lines)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.803379416282642</v>
+      </c>
+      <c r="F2">
+        <v>0.17</v>
+      </c>
+      <c r="G2">
+        <v>12.8</v>
+      </c>
+      <c r="H2">
+        <v>67.6267936068747</v>
+      </c>
+      <c r="I2">
+        <v>64.88800000000001</v>
+      </c>
+      <c r="J2">
+        <v>78.4817936068747</v>
+      </c>
+      <c r="K2">
+        <v>52.3</v>
+      </c>
+      <c r="L2">
+        <v>11.067</v>
+      </c>
+      <c r="M2">
+        <v>0.337117905169306</v>
+      </c>
+      <c r="N2">
+        <v>0.285446404739281</v>
+      </c>
+      <c r="O2">
+        <v>0.153388743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.04788</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>1.08782377823314</v>
+      </c>
+      <c r="T2">
+        <v>0.33410458402323</v>
+      </c>
+      <c r="U2">
+        <v>3.93983862763294</v>
+      </c>
+      <c r="V2">
+        <v>1.1090810629778</v>
+      </c>
+      <c r="W2">
+        <v>3.614348965392609</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>12.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.2662605952628563</v>
+      </c>
+      <c r="AC2">
+        <v>0.2018272935779817</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>4.69</v>
+      </c>
+      <c r="AH2">
+        <v>2.17</v>
+      </c>
+      <c r="AI2">
+        <v>10.12</v>
+      </c>
+      <c r="AJ2">
+        <v>52.3</v>
+      </c>
+      <c r="AK2">
+        <v>52.3</v>
+      </c>
+      <c r="AL2">
+        <v>5.81</v>
+      </c>
+      <c r="AM2">
+        <v>52.3</v>
+      </c>
+      <c r="AN2">
+        <v>0.212</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2943283619050052</v>
+      </c>
+      <c r="C2">
+        <v>75.96583055843386</v>
+      </c>
+      <c r="D2">
+        <v>75.75383055843386</v>
+      </c>
+      <c r="E2">
+        <v>-52.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.212</v>
+      </c>
+      <c r="H2">
+        <v>12.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>4.69</v>
+      </c>
+      <c r="K2">
+        <v>2.17</v>
+      </c>
+      <c r="L2">
+        <v>2.52</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.52</v>
+      </c>
+      <c r="O2">
+        <v>0.6048</v>
+      </c>
+      <c r="P2">
+        <v>1.9152</v>
+      </c>
+      <c r="Q2">
+        <v>4.0852</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2943283619050052</v>
+      </c>
+      <c r="T2">
+        <v>0.9596927463214897</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2936744138364332</v>
+      </c>
+      <c r="C3">
+        <v>75.5091971503367</v>
+      </c>
+      <c r="D3">
+        <v>75.9481971503367</v>
+      </c>
+      <c r="E3">
+        <v>-51.64899999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.6509999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0.212</v>
+      </c>
+      <c r="H3">
+        <v>12.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>4.69</v>
+      </c>
+      <c r="K3">
+        <v>2.17</v>
+      </c>
+      <c r="L3">
+        <v>2.52</v>
+      </c>
+      <c r="M3">
+        <v>0.0297507</v>
+      </c>
+      <c r="N3">
+        <v>2.4902493</v>
+      </c>
+      <c r="O3">
+        <v>0.5976598319999999</v>
+      </c>
+      <c r="P3">
+        <v>1.892589468</v>
+      </c>
+      <c r="Q3">
+        <v>4.062589468000001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.296289993774175</v>
+      </c>
+      <c r="T3">
+        <v>0.9670600845760789</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>84.70388932025129</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2930204657678612</v>
+      </c>
+      <c r="C4">
+        <v>75.05356370624308</v>
+      </c>
+      <c r="D4">
+        <v>76.14356370624309</v>
+      </c>
+      <c r="E4">
+        <v>-50.998</v>
+      </c>
+      <c r="F4">
+        <v>1.302</v>
+      </c>
+      <c r="G4">
+        <v>0.212</v>
+      </c>
+      <c r="H4">
+        <v>12.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>4.69</v>
+      </c>
+      <c r="K4">
+        <v>2.17</v>
+      </c>
+      <c r="L4">
+        <v>2.52</v>
+      </c>
+      <c r="M4">
+        <v>0.0595014</v>
+      </c>
+      <c r="N4">
+        <v>2.4604986</v>
+      </c>
+      <c r="O4">
+        <v>0.590519664</v>
+      </c>
+      <c r="P4">
+        <v>1.869978936</v>
+      </c>
+      <c r="Q4">
+        <v>4.039978936000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2982916589467972</v>
+      </c>
+      <c r="T4">
+        <v>0.9745777766725985</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>42.35194466012565</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2923665176992892</v>
+      </c>
+      <c r="C5">
+        <v>74.5989379628748</v>
+      </c>
+      <c r="D5">
+        <v>76.3399379628748</v>
+      </c>
+      <c r="E5">
+        <v>-50.34699999999999</v>
+      </c>
+      <c r="F5">
+        <v>1.953</v>
+      </c>
+      <c r="G5">
+        <v>0.212</v>
+      </c>
+      <c r="H5">
+        <v>12.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>4.69</v>
+      </c>
+      <c r="K5">
+        <v>2.17</v>
+      </c>
+      <c r="L5">
+        <v>2.52</v>
+      </c>
+      <c r="M5">
+        <v>0.0892521</v>
+      </c>
+      <c r="N5">
+        <v>2.4307479</v>
+      </c>
+      <c r="O5">
+        <v>0.5833794959999999</v>
+      </c>
+      <c r="P5">
+        <v>1.847368404</v>
+      </c>
+      <c r="Q5">
+        <v>4.017368404000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.3003345955662776</v>
+      </c>
+      <c r="T5">
+        <v>0.9822504727298712</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>28.2346297734171</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2917125696307172</v>
+      </c>
+      <c r="C6">
+        <v>74.14532773697194</v>
+      </c>
+      <c r="D6">
+        <v>76.53732773697193</v>
+      </c>
+      <c r="E6">
+        <v>-49.696</v>
+      </c>
+      <c r="F6">
+        <v>2.604</v>
+      </c>
+      <c r="G6">
+        <v>0.212</v>
+      </c>
+      <c r="H6">
+        <v>12.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>4.69</v>
+      </c>
+      <c r="K6">
+        <v>2.17</v>
+      </c>
+      <c r="L6">
+        <v>2.52</v>
+      </c>
+      <c r="M6">
+        <v>0.1190028</v>
+      </c>
+      <c r="N6">
+        <v>2.4009972</v>
+      </c>
+      <c r="O6">
+        <v>0.576239328</v>
+      </c>
+      <c r="P6">
+        <v>1.824757872</v>
+      </c>
+      <c r="Q6">
+        <v>3.994757872</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.3024200933653304</v>
+      </c>
+      <c r="T6">
+        <v>0.9900830166216703</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>21.17597233006282</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2910586215621452</v>
+      </c>
+      <c r="C7">
+        <v>73.69274092633016</v>
+      </c>
+      <c r="D7">
+        <v>76.73574092633015</v>
+      </c>
+      <c r="E7">
+        <v>-49.04499999999999</v>
+      </c>
+      <c r="F7">
+        <v>3.255</v>
+      </c>
+      <c r="G7">
+        <v>0.212</v>
+      </c>
+      <c r="H7">
+        <v>12.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>4.69</v>
+      </c>
+      <c r="K7">
+        <v>2.17</v>
+      </c>
+      <c r="L7">
+        <v>2.52</v>
+      </c>
+      <c r="M7">
+        <v>0.1487535</v>
+      </c>
+      <c r="N7">
+        <v>2.3712465</v>
+      </c>
+      <c r="O7">
+        <v>0.5690991599999999</v>
+      </c>
+      <c r="P7">
+        <v>1.80214734</v>
+      </c>
+      <c r="Q7">
+        <v>3.97214734</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.3045494963812055</v>
+      </c>
+      <c r="T7">
+        <v>0.9980804561743494</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>16.94077786405025</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2904046734935732</v>
+      </c>
+      <c r="C8">
+        <v>73.24118551085412</v>
+      </c>
+      <c r="D8">
+        <v>76.93518551085413</v>
+      </c>
+      <c r="E8">
+        <v>-48.394</v>
+      </c>
+      <c r="F8">
+        <v>3.906</v>
+      </c>
+      <c r="G8">
+        <v>0.212</v>
+      </c>
+      <c r="H8">
+        <v>12.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>4.69</v>
+      </c>
+      <c r="K8">
+        <v>2.17</v>
+      </c>
+      <c r="L8">
+        <v>2.52</v>
+      </c>
+      <c r="M8">
+        <v>0.1785042</v>
+      </c>
+      <c r="N8">
+        <v>2.3414958</v>
+      </c>
+      <c r="O8">
+        <v>0.561958992</v>
+      </c>
+      <c r="P8">
+        <v>1.779536808</v>
+      </c>
+      <c r="Q8">
+        <v>3.949536808</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.3067242058442268</v>
+      </c>
+      <c r="T8">
+        <v>1.006248054015383</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>14.11731488670855</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2898358454250011</v>
+      </c>
+      <c r="C9">
+        <v>72.76451477010903</v>
+      </c>
+      <c r="D9">
+        <v>77.10951477010903</v>
+      </c>
+      <c r="E9">
+        <v>-47.74299999999999</v>
+      </c>
+      <c r="F9">
+        <v>4.557</v>
+      </c>
+      <c r="G9">
+        <v>0.212</v>
+      </c>
+      <c r="H9">
+        <v>12.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>4.69</v>
+      </c>
+      <c r="K9">
+        <v>2.17</v>
+      </c>
+      <c r="L9">
+        <v>2.52</v>
+      </c>
+      <c r="M9">
+        <v>0.2155461</v>
+      </c>
+      <c r="N9">
+        <v>2.3044539</v>
+      </c>
+      <c r="O9">
+        <v>0.553068936</v>
+      </c>
+      <c r="P9">
+        <v>1.751384964</v>
+      </c>
+      <c r="Q9">
+        <v>3.921384964</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.3089456832526894</v>
+      </c>
+      <c r="T9">
+        <v>1.014591299121816</v>
+      </c>
+      <c r="U9">
+        <v>0.0473</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.035948</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>11.69123449693592</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2894250973564291</v>
+      </c>
+      <c r="C10">
+        <v>72.23988912205715</v>
+      </c>
+      <c r="D10">
+        <v>77.23588912205715</v>
+      </c>
+      <c r="E10">
+        <v>-47.092</v>
+      </c>
+      <c r="F10">
+        <v>5.207999999999999</v>
+      </c>
+      <c r="G10">
+        <v>0.212</v>
+      </c>
+      <c r="H10">
+        <v>12.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>4.69</v>
+      </c>
+      <c r="K10">
+        <v>2.17</v>
+      </c>
+      <c r="L10">
+        <v>2.52</v>
+      </c>
+      <c r="M10">
+        <v>0.2661287999999999</v>
+      </c>
+      <c r="N10">
+        <v>2.2538712</v>
+      </c>
+      <c r="O10">
+        <v>0.5409290879999999</v>
+      </c>
+      <c r="P10">
+        <v>1.712942112</v>
+      </c>
+      <c r="Q10">
+        <v>3.882942112</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.3112154536482925</v>
+      </c>
+      <c r="T10">
+        <v>1.023115919121866</v>
+      </c>
+      <c r="U10">
+        <v>0.0511</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.038836</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>9.469099173032006</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2888121892878571</v>
+      </c>
+      <c r="C11">
+        <v>71.77823388865065</v>
+      </c>
+      <c r="D11">
+        <v>77.42523388865064</v>
+      </c>
+      <c r="E11">
+        <v>-46.441</v>
+      </c>
+      <c r="F11">
+        <v>5.858999999999999</v>
+      </c>
+      <c r="G11">
+        <v>0.212</v>
+      </c>
+      <c r="H11">
+        <v>12.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>4.69</v>
+      </c>
+      <c r="K11">
+        <v>2.17</v>
+      </c>
+      <c r="L11">
+        <v>2.52</v>
+      </c>
+      <c r="M11">
+        <v>0.2993949</v>
+      </c>
+      <c r="N11">
+        <v>2.2206051</v>
+      </c>
+      <c r="O11">
+        <v>0.532945224</v>
+      </c>
+      <c r="P11">
+        <v>1.687659876</v>
+      </c>
+      <c r="Q11">
+        <v>3.857659876</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.3135351091075353</v>
+      </c>
+      <c r="T11">
+        <v>1.031827893407632</v>
+      </c>
+      <c r="U11">
+        <v>0.0511</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.038836</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>8.416977042695118</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2883436812192851</v>
+      </c>
+      <c r="C12">
+        <v>71.27259660274811</v>
+      </c>
+      <c r="D12">
+        <v>77.57059660274811</v>
+      </c>
+      <c r="E12">
+        <v>-45.79</v>
+      </c>
+      <c r="F12">
+        <v>6.51</v>
+      </c>
+      <c r="G12">
+        <v>0.212</v>
+      </c>
+      <c r="H12">
+        <v>12.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>4.69</v>
+      </c>
+      <c r="K12">
+        <v>2.17</v>
+      </c>
+      <c r="L12">
+        <v>2.52</v>
+      </c>
+      <c r="M12">
+        <v>0.34503</v>
+      </c>
+      <c r="N12">
+        <v>2.17497</v>
+      </c>
+      <c r="O12">
+        <v>0.5219928</v>
+      </c>
+      <c r="P12">
+        <v>1.6529772</v>
+      </c>
+      <c r="Q12">
+        <v>3.8229772</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.3159063124658724</v>
+      </c>
+      <c r="T12">
+        <v>1.040733467121971</v>
+      </c>
+      <c r="U12">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.04028</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>7.303712720632989</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2877452131507131</v>
+      </c>
+      <c r="C13">
+        <v>70.80807749362074</v>
+      </c>
+      <c r="D13">
+        <v>77.75707749362074</v>
+      </c>
+      <c r="E13">
+        <v>-45.139</v>
+      </c>
+      <c r="F13">
+        <v>7.161</v>
+      </c>
+      <c r="G13">
+        <v>0.212</v>
+      </c>
+      <c r="H13">
+        <v>12.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>4.69</v>
+      </c>
+      <c r="K13">
+        <v>2.17</v>
+      </c>
+      <c r="L13">
+        <v>2.52</v>
+      </c>
+      <c r="M13">
+        <v>0.379533</v>
+      </c>
+      <c r="N13">
+        <v>2.140467</v>
+      </c>
+      <c r="O13">
+        <v>0.51371208</v>
+      </c>
+      <c r="P13">
+        <v>1.62675492</v>
+      </c>
+      <c r="Q13">
+        <v>3.796754920000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.3183308012929361</v>
+      </c>
+      <c r="T13">
+        <v>1.049839166088317</v>
+      </c>
+      <c r="U13">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.04028</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.63973883693908</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2873291450821411</v>
+      </c>
+      <c r="C14">
+        <v>70.28725231492743</v>
+      </c>
+      <c r="D14">
+        <v>77.88725231492742</v>
+      </c>
+      <c r="E14">
+        <v>-44.488</v>
+      </c>
+      <c r="F14">
+        <v>7.811999999999999</v>
+      </c>
+      <c r="G14">
+        <v>0.212</v>
+      </c>
+      <c r="H14">
+        <v>12.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>4.69</v>
+      </c>
+      <c r="K14">
+        <v>2.17</v>
+      </c>
+      <c r="L14">
+        <v>2.52</v>
+      </c>
+      <c r="M14">
+        <v>0.42966</v>
+      </c>
+      <c r="N14">
+        <v>2.09034</v>
+      </c>
+      <c r="O14">
+        <v>0.5016815999999999</v>
+      </c>
+      <c r="P14">
+        <v>1.5886584</v>
+      </c>
+      <c r="Q14">
+        <v>3.7586584</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.3208103921387967</v>
+      </c>
+      <c r="T14">
+        <v>1.059151812758444</v>
+      </c>
+      <c r="U14">
+        <v>0.055</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.0418</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.865102639296188</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2867458770135691</v>
+      </c>
+      <c r="C15">
+        <v>69.81947434616787</v>
+      </c>
+      <c r="D15">
+        <v>78.07047434616786</v>
+      </c>
+      <c r="E15">
+        <v>-43.837</v>
+      </c>
+      <c r="F15">
+        <v>8.462999999999999</v>
+      </c>
+      <c r="G15">
+        <v>0.212</v>
+      </c>
+      <c r="H15">
+        <v>12.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>4.69</v>
+      </c>
+      <c r="K15">
+        <v>2.17</v>
+      </c>
+      <c r="L15">
+        <v>2.52</v>
+      </c>
+      <c r="M15">
+        <v>0.465465</v>
+      </c>
+      <c r="N15">
+        <v>2.054535</v>
+      </c>
+      <c r="O15">
+        <v>0.4930884</v>
+      </c>
+      <c r="P15">
+        <v>1.5614466</v>
+      </c>
+      <c r="Q15">
+        <v>3.7314466</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.3233469850730679</v>
+      </c>
+      <c r="T15">
+        <v>1.068678543260068</v>
+      </c>
+      <c r="U15">
+        <v>0.055</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.0418</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.413940897811866</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2861626089449971</v>
+      </c>
+      <c r="C16">
+        <v>69.35256043330365</v>
+      </c>
+      <c r="D16">
+        <v>78.25456043330365</v>
+      </c>
+      <c r="E16">
+        <v>-43.18599999999999</v>
+      </c>
+      <c r="F16">
+        <v>9.114000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.212</v>
+      </c>
+      <c r="H16">
+        <v>12.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>4.69</v>
+      </c>
+      <c r="K16">
+        <v>2.17</v>
+      </c>
+      <c r="L16">
+        <v>2.52</v>
+      </c>
+      <c r="M16">
+        <v>0.50127</v>
+      </c>
+      <c r="N16">
+        <v>2.01873</v>
+      </c>
+      <c r="O16">
+        <v>0.4844952</v>
+      </c>
+      <c r="P16">
+        <v>1.5342348</v>
+      </c>
+      <c r="Q16">
+        <v>3.7042348</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.3259425685406943</v>
+      </c>
+      <c r="T16">
+        <v>1.078426825633823</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.0418</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.027230833682447</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.285579340876425</v>
+      </c>
+      <c r="C17">
+        <v>68.88651670297676</v>
+      </c>
+      <c r="D17">
+        <v>78.43951670297676</v>
+      </c>
+      <c r="E17">
+        <v>-42.535</v>
+      </c>
+      <c r="F17">
+        <v>9.764999999999999</v>
+      </c>
+      <c r="G17">
+        <v>0.212</v>
+      </c>
+      <c r="H17">
+        <v>12.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>4.69</v>
+      </c>
+      <c r="K17">
+        <v>2.17</v>
+      </c>
+      <c r="L17">
+        <v>2.52</v>
+      </c>
+      <c r="M17">
+        <v>0.537075</v>
+      </c>
+      <c r="N17">
+        <v>1.982925</v>
+      </c>
+      <c r="O17">
+        <v>0.475902</v>
+      </c>
+      <c r="P17">
+        <v>1.507023</v>
+      </c>
+      <c r="Q17">
+        <v>3.677023</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.3285992245605</v>
+      </c>
+      <c r="T17">
+        <v>1.088404479357548</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.0418</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.69208211143695</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.285458152807853</v>
+      </c>
+      <c r="C18">
+        <v>68.27405560153228</v>
+      </c>
+      <c r="D18">
+        <v>78.47805560153228</v>
+      </c>
+      <c r="E18">
+        <v>-41.884</v>
+      </c>
+      <c r="F18">
+        <v>10.416</v>
+      </c>
+      <c r="G18">
+        <v>0.212</v>
+      </c>
+      <c r="H18">
+        <v>12.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>4.69</v>
+      </c>
+      <c r="K18">
+        <v>2.17</v>
+      </c>
+      <c r="L18">
+        <v>2.52</v>
+      </c>
+      <c r="M18">
+        <v>0.6124607999999999</v>
+      </c>
+      <c r="N18">
+        <v>1.9075392</v>
+      </c>
+      <c r="O18">
+        <v>0.457809408</v>
+      </c>
+      <c r="P18">
+        <v>1.449729792</v>
+      </c>
+      <c r="Q18">
+        <v>3.619729792</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.3313191342950632</v>
+      </c>
+      <c r="T18">
+        <v>1.098619696265172</v>
+      </c>
+      <c r="U18">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.114549045424623</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.285446404739281</v>
+      </c>
+      <c r="C19">
+        <v>67.62679360687468</v>
+      </c>
+      <c r="D19">
+        <v>78.48179360687469</v>
+      </c>
+      <c r="E19">
+        <v>-41.233</v>
+      </c>
+      <c r="F19">
+        <v>11.067</v>
+      </c>
+      <c r="G19">
+        <v>0.212</v>
+      </c>
+      <c r="H19">
+        <v>12.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>4.69</v>
+      </c>
+      <c r="K19">
+        <v>2.17</v>
+      </c>
+      <c r="L19">
+        <v>2.52</v>
+      </c>
+      <c r="M19">
+        <v>0.697221</v>
+      </c>
+      <c r="N19">
+        <v>1.822779</v>
+      </c>
+      <c r="O19">
+        <v>0.43746696</v>
+      </c>
+      <c r="P19">
+        <v>1.38531204</v>
+      </c>
+      <c r="Q19">
+        <v>3.55531204</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.3341045840232301</v>
+      </c>
+      <c r="T19">
+        <v>1.109081062977799</v>
+      </c>
+      <c r="U19">
+        <v>0.063</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.04788</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.614348965392609</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.285895216670709</v>
+      </c>
+      <c r="C20">
+        <v>66.83324303124954</v>
+      </c>
+      <c r="D20">
+        <v>78.33924303124954</v>
+      </c>
+      <c r="E20">
+        <v>-40.582</v>
+      </c>
+      <c r="F20">
+        <v>11.718</v>
+      </c>
+      <c r="G20">
+        <v>0.212</v>
+      </c>
+      <c r="H20">
+        <v>12.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>4.69</v>
+      </c>
+      <c r="K20">
+        <v>2.17</v>
+      </c>
+      <c r="L20">
+        <v>2.52</v>
+      </c>
+      <c r="M20">
+        <v>0.8214317999999998</v>
+      </c>
+      <c r="N20">
+        <v>1.6985682</v>
+      </c>
+      <c r="O20">
+        <v>0.407656368</v>
+      </c>
+      <c r="P20">
+        <v>1.290911832</v>
+      </c>
+      <c r="Q20">
+        <v>3.460911832000001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.3369579715496451</v>
+      </c>
+      <c r="T20">
+        <v>1.119797584976099</v>
+      </c>
+      <c r="U20">
+        <v>0.0701</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.053276</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.067814029113556</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.288502428602137</v>
+      </c>
+      <c r="C21">
+        <v>65.36428138676929</v>
+      </c>
+      <c r="D21">
+        <v>77.52128138676929</v>
+      </c>
+      <c r="E21">
+        <v>-39.931</v>
+      </c>
+      <c r="F21">
+        <v>12.369</v>
+      </c>
+      <c r="G21">
+        <v>0.212</v>
+      </c>
+      <c r="H21">
+        <v>12.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>4.69</v>
+      </c>
+      <c r="K21">
+        <v>2.17</v>
+      </c>
+      <c r="L21">
+        <v>2.52</v>
+      </c>
+      <c r="M21">
+        <v>1.1305266</v>
+      </c>
+      <c r="N21">
+        <v>1.3894734</v>
+      </c>
+      <c r="O21">
+        <v>0.333473616</v>
+      </c>
+      <c r="P21">
+        <v>1.055999784</v>
+      </c>
+      <c r="Q21">
+        <v>3.225999784</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.339881813089058</v>
+      </c>
+      <c r="T21">
+        <v>1.130778712455839</v>
+      </c>
+      <c r="U21">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.229049718953982</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.288195800533565</v>
+      </c>
+      <c r="C22">
+        <v>64.80859253769486</v>
+      </c>
+      <c r="D22">
+        <v>77.61659253769486</v>
+      </c>
+      <c r="E22">
+        <v>-39.28</v>
+      </c>
+      <c r="F22">
+        <v>13.02</v>
+      </c>
+      <c r="G22">
+        <v>0.212</v>
+      </c>
+      <c r="H22">
+        <v>12.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>4.69</v>
+      </c>
+      <c r="K22">
+        <v>2.17</v>
+      </c>
+      <c r="L22">
+        <v>2.52</v>
+      </c>
+      <c r="M22">
+        <v>1.190028</v>
+      </c>
+      <c r="N22">
+        <v>1.329972</v>
+      </c>
+      <c r="O22">
+        <v>0.31919328</v>
+      </c>
+      <c r="P22">
+        <v>1.01077872</v>
+      </c>
+      <c r="Q22">
+        <v>3.18077872</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.3428787506669562</v>
+      </c>
+      <c r="T22">
+        <v>1.142034368122573</v>
+      </c>
+      <c r="U22">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.117597233006282</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.287889172464993</v>
+      </c>
+      <c r="C23">
+        <v>64.25313834413619</v>
+      </c>
+      <c r="D23">
+        <v>77.71213834413618</v>
+      </c>
+      <c r="E23">
+        <v>-38.629</v>
+      </c>
+      <c r="F23">
+        <v>13.671</v>
+      </c>
+      <c r="G23">
+        <v>0.212</v>
+      </c>
+      <c r="H23">
+        <v>12.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>4.69</v>
+      </c>
+      <c r="K23">
+        <v>2.17</v>
+      </c>
+      <c r="L23">
+        <v>2.52</v>
+      </c>
+      <c r="M23">
+        <v>1.2495294</v>
+      </c>
+      <c r="N23">
+        <v>1.2704706</v>
+      </c>
+      <c r="O23">
+        <v>0.304912944</v>
+      </c>
+      <c r="P23">
+        <v>0.9655576560000001</v>
+      </c>
+      <c r="Q23">
+        <v>3.135557656</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.3459515600822696</v>
+      </c>
+      <c r="T23">
+        <v>1.153574977097325</v>
+      </c>
+      <c r="U23">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.016759269529793</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.291110464396421</v>
+      </c>
+      <c r="C24">
+        <v>62.60997385020278</v>
+      </c>
+      <c r="D24">
+        <v>76.71997385020278</v>
+      </c>
+      <c r="E24">
+        <v>-37.97799999999999</v>
+      </c>
+      <c r="F24">
+        <v>14.322</v>
+      </c>
+      <c r="G24">
+        <v>0.212</v>
+      </c>
+      <c r="H24">
+        <v>12.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>4.69</v>
+      </c>
+      <c r="K24">
+        <v>2.17</v>
+      </c>
+      <c r="L24">
+        <v>2.52</v>
+      </c>
+      <c r="M24">
+        <v>1.611225</v>
+      </c>
+      <c r="N24">
+        <v>0.9087750000000001</v>
+      </c>
+      <c r="O24">
+        <v>0.218106</v>
+      </c>
+      <c r="P24">
+        <v>0.6906690000000001</v>
+      </c>
+      <c r="Q24">
+        <v>2.860669000000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.349103159482591</v>
+      </c>
+      <c r="T24">
+        <v>1.165411499122712</v>
+      </c>
+      <c r="U24">
+        <v>0.1125</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>1.564027370478983</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.3092570601249636</v>
+      </c>
+      <c r="C25">
+        <v>56.81136798211882</v>
+      </c>
+      <c r="D25">
+        <v>71.57236798211882</v>
+      </c>
+      <c r="E25">
+        <v>-37.327</v>
+      </c>
+      <c r="F25">
+        <v>14.973</v>
+      </c>
+      <c r="G25">
+        <v>0.212</v>
+      </c>
+      <c r="H25">
+        <v>12.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>4.69</v>
+      </c>
+      <c r="K25">
+        <v>2.17</v>
+      </c>
+      <c r="L25">
+        <v>2.52</v>
+      </c>
+      <c r="M25">
+        <v>2.9436918</v>
+      </c>
+      <c r="N25">
+        <v>-0.4236917999999998</v>
+      </c>
+      <c r="O25">
+        <v>-0.101686032</v>
+      </c>
+      <c r="P25">
+        <v>-0.3220057679999999</v>
+      </c>
+      <c r="Q25">
+        <v>1.847994232</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.3549732242929984</v>
+      </c>
+      <c r="T25">
+        <v>1.187457813578715</v>
+      </c>
+      <c r="U25">
+        <v>0.1966</v>
+      </c>
+      <c r="V25">
+        <v>0.2054562913141926</v>
+      </c>
+      <c r="W25">
+        <v>0.1562072931276297</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.8560678804758026</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.3108350601249636</v>
+      </c>
+      <c r="C26">
+        <v>55.74519650891277</v>
+      </c>
+      <c r="D26">
+        <v>71.15719650891276</v>
+      </c>
+      <c r="E26">
+        <v>-36.676</v>
+      </c>
+      <c r="F26">
+        <v>15.624</v>
+      </c>
+      <c r="G26">
+        <v>0.212</v>
+      </c>
+      <c r="H26">
+        <v>12.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>4.69</v>
+      </c>
+      <c r="K26">
+        <v>2.17</v>
+      </c>
+      <c r="L26">
+        <v>2.52</v>
+      </c>
+      <c r="M26">
+        <v>3.0716784</v>
+      </c>
+      <c r="N26">
+        <v>-0.5516783999999997</v>
+      </c>
+      <c r="O26">
+        <v>-0.1324028159999999</v>
+      </c>
+      <c r="P26">
+        <v>-0.4192755839999998</v>
+      </c>
+      <c r="Q26">
+        <v>1.750724416000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.3591333982968536</v>
+      </c>
+      <c r="T26">
+        <v>1.203082258494224</v>
+      </c>
+      <c r="U26">
+        <v>0.1966</v>
+      </c>
+      <c r="V26">
+        <v>0.1968956125094346</v>
+      </c>
+      <c r="W26">
+        <v>0.1578903225806452</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.8203983854559775</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.317684480341192</v>
+      </c>
+      <c r="C27">
+        <v>53.34657132840074</v>
+      </c>
+      <c r="D27">
+        <v>69.40957132840073</v>
+      </c>
+      <c r="E27">
+        <v>-36.025</v>
+      </c>
+      <c r="F27">
+        <v>16.275</v>
+      </c>
+      <c r="G27">
+        <v>0.212</v>
+      </c>
+      <c r="H27">
+        <v>12.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>4.69</v>
+      </c>
+      <c r="K27">
+        <v>2.17</v>
+      </c>
+      <c r="L27">
+        <v>2.52</v>
+      </c>
+      <c r="M27">
+        <v>3.479594999999999</v>
+      </c>
+      <c r="N27">
+        <v>-0.9595949999999993</v>
+      </c>
+      <c r="O27">
+        <v>-0.2303027999999998</v>
+      </c>
+      <c r="P27">
+        <v>-0.7292921999999995</v>
+      </c>
+      <c r="Q27">
+        <v>1.440707800000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.3646997372291162</v>
+      </c>
+      <c r="T27">
+        <v>1.223987863872171</v>
+      </c>
+      <c r="U27">
+        <v>0.2138</v>
+      </c>
+      <c r="V27">
+        <v>0.1738133317239507</v>
+      </c>
+      <c r="W27">
+        <v>0.1766387096774193</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.724222215516461</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.3194344803411919</v>
+      </c>
+      <c r="C28">
+        <v>52.26274229870694</v>
+      </c>
+      <c r="D28">
+        <v>68.97674229870694</v>
+      </c>
+      <c r="E28">
+        <v>-35.374</v>
+      </c>
+      <c r="F28">
+        <v>16.926</v>
+      </c>
+      <c r="G28">
+        <v>0.212</v>
+      </c>
+      <c r="H28">
+        <v>12.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>4.69</v>
+      </c>
+      <c r="K28">
+        <v>2.17</v>
+      </c>
+      <c r="L28">
+        <v>2.52</v>
+      </c>
+      <c r="M28">
+        <v>3.618778799999999</v>
+      </c>
+      <c r="N28">
+        <v>-1.098778799999999</v>
+      </c>
+      <c r="O28">
+        <v>-0.2637069119999998</v>
+      </c>
+      <c r="P28">
+        <v>-0.8350718879999995</v>
+      </c>
+      <c r="Q28">
+        <v>1.334928112000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.3691037877322123</v>
+      </c>
+      <c r="T28">
+        <v>1.240528240410984</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0.1671282035807218</v>
+      </c>
+      <c r="W28">
+        <v>0.1780679900744417</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.6963675149196742</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.321184480341192</v>
+      </c>
+      <c r="C29">
+        <v>51.18427794628612</v>
+      </c>
+      <c r="D29">
+        <v>68.54927794628611</v>
+      </c>
+      <c r="E29">
+        <v>-34.723</v>
+      </c>
+      <c r="F29">
+        <v>17.577</v>
+      </c>
+      <c r="G29">
+        <v>0.212</v>
+      </c>
+      <c r="H29">
+        <v>12.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>4.69</v>
+      </c>
+      <c r="K29">
+        <v>2.17</v>
+      </c>
+      <c r="L29">
+        <v>2.52</v>
+      </c>
+      <c r="M29">
+        <v>3.757962599999999</v>
+      </c>
+      <c r="N29">
+        <v>-1.237962599999999</v>
+      </c>
+      <c r="O29">
+        <v>-0.2971110239999998</v>
+      </c>
+      <c r="P29">
+        <v>-0.9408515759999996</v>
+      </c>
+      <c r="Q29">
+        <v>1.229148424000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.3736284971532016</v>
+      </c>
+      <c r="T29">
+        <v>1.257521777950861</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0.1609382701147691</v>
+      </c>
+      <c r="W29">
+        <v>0.1793913978494623</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.6705761254782048</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.322934480341192</v>
+      </c>
+      <c r="C30">
+        <v>50.11107914710498</v>
+      </c>
+      <c r="D30">
+        <v>68.12707914710498</v>
+      </c>
+      <c r="E30">
+        <v>-34.072</v>
+      </c>
+      <c r="F30">
+        <v>18.228</v>
+      </c>
+      <c r="G30">
+        <v>0.212</v>
+      </c>
+      <c r="H30">
+        <v>12.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>4.69</v>
+      </c>
+      <c r="K30">
+        <v>2.17</v>
+      </c>
+      <c r="L30">
+        <v>2.52</v>
+      </c>
+      <c r="M30">
+        <v>3.8971464</v>
+      </c>
+      <c r="N30">
+        <v>-1.3771464</v>
+      </c>
+      <c r="O30">
+        <v>-0.330515136</v>
+      </c>
+      <c r="P30">
+        <v>-1.046631264</v>
+      </c>
+      <c r="Q30">
+        <v>1.123368736</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.3782788929469961</v>
+      </c>
+      <c r="T30">
+        <v>1.274987358200178</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.1551904747535273</v>
+      </c>
+      <c r="W30">
+        <v>0.1806202764976959</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.6466269781396973</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.324684480341192</v>
+      </c>
+      <c r="C31">
+        <v>49.04304920422337</v>
+      </c>
+      <c r="D31">
+        <v>67.71004920422337</v>
+      </c>
+      <c r="E31">
+        <v>-33.421</v>
+      </c>
+      <c r="F31">
+        <v>18.879</v>
+      </c>
+      <c r="G31">
+        <v>0.212</v>
+      </c>
+      <c r="H31">
+        <v>12.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>4.69</v>
+      </c>
+      <c r="K31">
+        <v>2.17</v>
+      </c>
+      <c r="L31">
+        <v>2.52</v>
+      </c>
+      <c r="M31">
+        <v>4.036330199999999</v>
+      </c>
+      <c r="N31">
+        <v>-1.516330199999999</v>
+      </c>
+      <c r="O31">
+        <v>-0.3639192479999998</v>
+      </c>
+      <c r="P31">
+        <v>-1.152410951999999</v>
+      </c>
+      <c r="Q31">
+        <v>1.017589048000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.3830602858054044</v>
+      </c>
+      <c r="T31">
+        <v>1.292944926625533</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.1498390790723713</v>
+      </c>
+      <c r="W31">
+        <v>0.181764404894327</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.6243294961348802</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.3264344803411919</v>
+      </c>
+      <c r="C32">
+        <v>47.98009377396052</v>
+      </c>
+      <c r="D32">
+        <v>67.29809377396052</v>
+      </c>
+      <c r="E32">
+        <v>-32.77</v>
+      </c>
+      <c r="F32">
+        <v>19.53</v>
+      </c>
+      <c r="G32">
+        <v>0.212</v>
+      </c>
+      <c r="H32">
+        <v>12.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>4.69</v>
+      </c>
+      <c r="K32">
+        <v>2.17</v>
+      </c>
+      <c r="L32">
+        <v>2.52</v>
+      </c>
+      <c r="M32">
+        <v>4.175514</v>
+      </c>
+      <c r="N32">
+        <v>-1.655514</v>
+      </c>
+      <c r="O32">
+        <v>-0.3973233599999999</v>
+      </c>
+      <c r="P32">
+        <v>-1.25819064</v>
+      </c>
+      <c r="Q32">
+        <v>0.9118093600000006</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.3879782898883387</v>
+      </c>
+      <c r="T32">
+        <v>1.311415568434469</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.1448444431032922</v>
+      </c>
+      <c r="W32">
+        <v>0.1828322580645161</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.6035185129303842</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.328184480341192</v>
+      </c>
+      <c r="C33">
+        <v>46.92212079474069</v>
+      </c>
+      <c r="D33">
+        <v>66.89112079474069</v>
+      </c>
+      <c r="E33">
+        <v>-32.119</v>
+      </c>
+      <c r="F33">
+        <v>20.181</v>
+      </c>
+      <c r="G33">
+        <v>0.212</v>
+      </c>
+      <c r="H33">
+        <v>12.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>4.69</v>
+      </c>
+      <c r="K33">
+        <v>2.17</v>
+      </c>
+      <c r="L33">
+        <v>2.52</v>
+      </c>
+      <c r="M33">
+        <v>4.314697799999999</v>
+      </c>
+      <c r="N33">
+        <v>-1.794697799999999</v>
+      </c>
+      <c r="O33">
+        <v>-0.4307274719999998</v>
+      </c>
+      <c r="P33">
+        <v>-1.363970328</v>
+      </c>
+      <c r="Q33">
+        <v>0.8060296720000009</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.3930388448142567</v>
+      </c>
+      <c r="T33">
+        <v>1.330421591165403</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.1401720417128634</v>
+      </c>
+      <c r="W33">
+        <v>0.1838312174817898</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5840501738035977</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.3299344803411919</v>
+      </c>
+      <c r="C34">
+        <v>45.86904041850492</v>
+      </c>
+      <c r="D34">
+        <v>66.48904041850491</v>
+      </c>
+      <c r="E34">
+        <v>-31.468</v>
+      </c>
+      <c r="F34">
+        <v>20.832</v>
+      </c>
+      <c r="G34">
+        <v>0.212</v>
+      </c>
+      <c r="H34">
+        <v>12.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>4.69</v>
+      </c>
+      <c r="K34">
+        <v>2.17</v>
+      </c>
+      <c r="L34">
+        <v>2.52</v>
+      </c>
+      <c r="M34">
+        <v>4.453881599999999</v>
+      </c>
+      <c r="N34">
+        <v>-1.933881599999999</v>
+      </c>
+      <c r="O34">
+        <v>-0.4641315839999998</v>
+      </c>
+      <c r="P34">
+        <v>-1.469750015999999</v>
+      </c>
+      <c r="Q34">
+        <v>0.7002499840000012</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.398248239590937</v>
+      </c>
+      <c r="T34">
+        <v>1.349986614564894</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1357916654093365</v>
+      </c>
+      <c r="W34">
+        <v>0.1847677419354838</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.5657986058722353</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.331684480341192</v>
+      </c>
+      <c r="C35">
+        <v>44.8207649445814</v>
+      </c>
+      <c r="D35">
+        <v>66.0917649445814</v>
+      </c>
+      <c r="E35">
+        <v>-30.817</v>
+      </c>
+      <c r="F35">
+        <v>21.483</v>
+      </c>
+      <c r="G35">
+        <v>0.212</v>
+      </c>
+      <c r="H35">
+        <v>12.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>4.69</v>
+      </c>
+      <c r="K35">
+        <v>2.17</v>
+      </c>
+      <c r="L35">
+        <v>2.52</v>
+      </c>
+      <c r="M35">
+        <v>4.5930654</v>
+      </c>
+      <c r="N35">
+        <v>-2.0730654</v>
+      </c>
+      <c r="O35">
+        <v>-0.4975356959999999</v>
+      </c>
+      <c r="P35">
+        <v>-1.575529704</v>
+      </c>
+      <c r="Q35">
+        <v>0.5944702960000008</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.4036131386893091</v>
+      </c>
+      <c r="T35">
+        <v>1.370135668513624</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1316767664575384</v>
+      </c>
+      <c r="W35">
+        <v>0.1856475073313783</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5486531935730765</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.3334344803411919</v>
+      </c>
+      <c r="C36">
+        <v>43.77720875591307</v>
+      </c>
+      <c r="D36">
+        <v>65.69920875591306</v>
+      </c>
+      <c r="E36">
+        <v>-30.166</v>
+      </c>
+      <c r="F36">
+        <v>22.134</v>
+      </c>
+      <c r="G36">
+        <v>0.212</v>
+      </c>
+      <c r="H36">
+        <v>12.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>4.69</v>
+      </c>
+      <c r="K36">
+        <v>2.17</v>
+      </c>
+      <c r="L36">
+        <v>2.52</v>
+      </c>
+      <c r="M36">
+        <v>4.7322492</v>
+      </c>
+      <c r="N36">
+        <v>-2.2122492</v>
+      </c>
+      <c r="O36">
+        <v>-0.530939808</v>
+      </c>
+      <c r="P36">
+        <v>-1.681309392</v>
+      </c>
+      <c r="Q36">
+        <v>0.4886906080000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.4091406104876321</v>
+      </c>
+      <c r="T36">
+        <v>1.39089529985474</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1278039203852578</v>
+      </c>
+      <c r="W36">
+        <v>0.1864755218216319</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5325163349385742</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.335184480341192</v>
+      </c>
+      <c r="C37">
+        <v>42.73828825754387</v>
+      </c>
+      <c r="D37">
+        <v>65.31128825754386</v>
+      </c>
+      <c r="E37">
+        <v>-29.515</v>
+      </c>
+      <c r="F37">
+        <v>22.785</v>
+      </c>
+      <c r="G37">
+        <v>0.212</v>
+      </c>
+      <c r="H37">
+        <v>12.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>4.69</v>
+      </c>
+      <c r="K37">
+        <v>2.17</v>
+      </c>
+      <c r="L37">
+        <v>2.52</v>
+      </c>
+      <c r="M37">
+        <v>4.871433</v>
+      </c>
+      <c r="N37">
+        <v>-2.351433</v>
+      </c>
+      <c r="O37">
+        <v>-0.5643439199999999</v>
+      </c>
+      <c r="P37">
+        <v>-1.78708908</v>
+      </c>
+      <c r="Q37">
+        <v>0.3829109200000005</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.4148381583412879</v>
+      </c>
+      <c r="T37">
+        <v>1.412293689083274</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1241523798028219</v>
+      </c>
+      <c r="W37">
+        <v>0.1872562211981567</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.517301582511758</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.3369344803411919</v>
+      </c>
+      <c r="C38">
+        <v>41.70392181727203</v>
+      </c>
+      <c r="D38">
+        <v>64.92792181727202</v>
+      </c>
+      <c r="E38">
+        <v>-28.864</v>
+      </c>
+      <c r="F38">
+        <v>23.436</v>
+      </c>
+      <c r="G38">
+        <v>0.212</v>
+      </c>
+      <c r="H38">
+        <v>12.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>4.69</v>
+      </c>
+      <c r="K38">
+        <v>2.17</v>
+      </c>
+      <c r="L38">
+        <v>2.52</v>
+      </c>
+      <c r="M38">
+        <v>5.010616799999999</v>
+      </c>
+      <c r="N38">
+        <v>-2.490616799999999</v>
+      </c>
+      <c r="O38">
+        <v>-0.5977480319999998</v>
+      </c>
+      <c r="P38">
+        <v>-1.892868768</v>
+      </c>
+      <c r="Q38">
+        <v>0.2771312320000008</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.4207137545653705</v>
+      </c>
+      <c r="T38">
+        <v>1.4343607779752</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1207037025860768</v>
+      </c>
+      <c r="W38">
+        <v>0.1879935483870968</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5029320941086535</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.3490969132330647</v>
+      </c>
+      <c r="C39">
+        <v>38.50799965326004</v>
+      </c>
+      <c r="D39">
+        <v>62.38299965326004</v>
+      </c>
+      <c r="E39">
+        <v>-28.213</v>
+      </c>
+      <c r="F39">
+        <v>24.087</v>
+      </c>
+      <c r="G39">
+        <v>0.212</v>
+      </c>
+      <c r="H39">
+        <v>12.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>4.69</v>
+      </c>
+      <c r="K39">
+        <v>2.17</v>
+      </c>
+      <c r="L39">
+        <v>2.52</v>
+      </c>
+      <c r="M39">
+        <v>5.7519756</v>
+      </c>
+      <c r="N39">
+        <v>-3.2319756</v>
+      </c>
+      <c r="O39">
+        <v>-0.7756741439999999</v>
+      </c>
+      <c r="P39">
+        <v>-2.456301456</v>
+      </c>
+      <c r="Q39">
+        <v>-0.2863014559999995</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.4286210092281109</v>
+      </c>
+      <c r="T39">
+        <v>1.464058205245406</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.1051464821930051</v>
+      </c>
+      <c r="W39">
+        <v>0.2136910200523104</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.4381103424708548</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.3510969132330647</v>
+      </c>
+      <c r="C40">
+        <v>37.45748882231753</v>
+      </c>
+      <c r="D40">
+        <v>61.98348882231753</v>
+      </c>
+      <c r="E40">
+        <v>-27.562</v>
+      </c>
+      <c r="F40">
+        <v>24.738</v>
+      </c>
+      <c r="G40">
+        <v>0.212</v>
+      </c>
+      <c r="H40">
+        <v>12.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>4.69</v>
+      </c>
+      <c r="K40">
+        <v>2.17</v>
+      </c>
+      <c r="L40">
+        <v>2.52</v>
+      </c>
+      <c r="M40">
+        <v>5.907434400000001</v>
+      </c>
+      <c r="N40">
+        <v>-3.387434400000001</v>
+      </c>
+      <c r="O40">
+        <v>-0.8129842560000001</v>
+      </c>
+      <c r="P40">
+        <v>-2.574450144</v>
+      </c>
+      <c r="Q40">
+        <v>-0.4044501440000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.4349084448608224</v>
+      </c>
+      <c r="T40">
+        <v>1.487672047265493</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.1023794695037155</v>
+      </c>
+      <c r="W40">
+        <v>0.2143517826825128</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.426581122932148</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.3530969132330647</v>
+      </c>
+      <c r="C41">
+        <v>36.41206249350179</v>
+      </c>
+      <c r="D41">
+        <v>61.58906249350179</v>
+      </c>
+      <c r="E41">
+        <v>-26.911</v>
+      </c>
+      <c r="F41">
+        <v>25.389</v>
+      </c>
+      <c r="G41">
+        <v>0.212</v>
+      </c>
+      <c r="H41">
+        <v>12.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>4.69</v>
+      </c>
+      <c r="K41">
+        <v>2.17</v>
+      </c>
+      <c r="L41">
+        <v>2.52</v>
+      </c>
+      <c r="M41">
+        <v>6.0628932</v>
+      </c>
+      <c r="N41">
+        <v>-3.5428932</v>
+      </c>
+      <c r="O41">
+        <v>-0.850294368</v>
+      </c>
+      <c r="P41">
+        <v>-2.692598832</v>
+      </c>
+      <c r="Q41">
+        <v>-0.5225988319999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.4414020259241145</v>
+      </c>
+      <c r="T41">
+        <v>1.512060113614108</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.09975435490105615</v>
+      </c>
+      <c r="W41">
+        <v>0.2149786600496278</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.4156431454210673</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.3550969132330647</v>
+      </c>
+      <c r="C42">
+        <v>35.37162421625804</v>
+      </c>
+      <c r="D42">
+        <v>61.19962421625804</v>
+      </c>
+      <c r="E42">
+        <v>-26.26</v>
+      </c>
+      <c r="F42">
+        <v>26.04</v>
+      </c>
+      <c r="G42">
+        <v>0.212</v>
+      </c>
+      <c r="H42">
+        <v>12.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>4.69</v>
+      </c>
+      <c r="K42">
+        <v>2.17</v>
+      </c>
+      <c r="L42">
+        <v>2.52</v>
+      </c>
+      <c r="M42">
+        <v>6.218352</v>
+      </c>
+      <c r="N42">
+        <v>-3.698352</v>
+      </c>
+      <c r="O42">
+        <v>-0.88760448</v>
+      </c>
+      <c r="P42">
+        <v>-2.81074752</v>
+      </c>
+      <c r="Q42">
+        <v>-0.6407475200000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.4481120596895165</v>
+      </c>
+      <c r="T42">
+        <v>1.537261115507676</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.09726049602852974</v>
+      </c>
+      <c r="W42">
+        <v>0.2155741935483871</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.4052520667855406</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.3570969132330647</v>
+      </c>
+      <c r="C43">
+        <v>34.3360799641971</v>
+      </c>
+      <c r="D43">
+        <v>60.8150799641971</v>
+      </c>
+      <c r="E43">
+        <v>-25.609</v>
+      </c>
+      <c r="F43">
+        <v>26.691</v>
+      </c>
+      <c r="G43">
+        <v>0.212</v>
+      </c>
+      <c r="H43">
+        <v>12.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>4.69</v>
+      </c>
+      <c r="K43">
+        <v>2.17</v>
+      </c>
+      <c r="L43">
+        <v>2.52</v>
+      </c>
+      <c r="M43">
+        <v>6.3738108</v>
+      </c>
+      <c r="N43">
+        <v>-3.8538108</v>
+      </c>
+      <c r="O43">
+        <v>-0.924914592</v>
+      </c>
+      <c r="P43">
+        <v>-2.928896208</v>
+      </c>
+      <c r="Q43">
+        <v>-0.7588962079999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.4550495522266269</v>
+      </c>
+      <c r="T43">
+        <v>1.563316388651874</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.0948882888083217</v>
+      </c>
+      <c r="W43">
+        <v>0.2161406766325728</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3953678700346738</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.3590969132330647</v>
+      </c>
+      <c r="C44">
+        <v>33.30533805941049</v>
+      </c>
+      <c r="D44">
+        <v>60.43533805941048</v>
+      </c>
+      <c r="E44">
+        <v>-24.958</v>
+      </c>
+      <c r="F44">
+        <v>27.342</v>
+      </c>
+      <c r="G44">
+        <v>0.212</v>
+      </c>
+      <c r="H44">
+        <v>12.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>4.69</v>
+      </c>
+      <c r="K44">
+        <v>2.17</v>
+      </c>
+      <c r="L44">
+        <v>2.52</v>
+      </c>
+      <c r="M44">
+        <v>6.529269599999999</v>
+      </c>
+      <c r="N44">
+        <v>-4.0092696</v>
+      </c>
+      <c r="O44">
+        <v>-0.9622247039999999</v>
+      </c>
+      <c r="P44">
+        <v>-3.047044896</v>
+      </c>
+      <c r="Q44">
+        <v>-0.8770448959999992</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.4622262686443273</v>
+      </c>
+      <c r="T44">
+        <v>1.590270119490699</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.092629043836695</v>
+      </c>
+      <c r="W44">
+        <v>0.2166801843317973</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3859543493195625</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.3610969132330647</v>
+      </c>
+      <c r="C45">
+        <v>32.27930909960344</v>
+      </c>
+      <c r="D45">
+        <v>60.06030909960343</v>
+      </c>
+      <c r="E45">
+        <v>-24.307</v>
+      </c>
+      <c r="F45">
+        <v>27.993</v>
+      </c>
+      <c r="G45">
+        <v>0.212</v>
+      </c>
+      <c r="H45">
+        <v>12.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>4.69</v>
+      </c>
+      <c r="K45">
+        <v>2.17</v>
+      </c>
+      <c r="L45">
+        <v>2.52</v>
+      </c>
+      <c r="M45">
+        <v>6.6847284</v>
+      </c>
+      <c r="N45">
+        <v>-4.1647284</v>
+      </c>
+      <c r="O45">
+        <v>-0.9995348159999998</v>
+      </c>
+      <c r="P45">
+        <v>-3.165193584</v>
+      </c>
+      <c r="Q45">
+        <v>-0.9951935839999995</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.4696547996731751</v>
+      </c>
+      <c r="T45">
+        <v>1.618169595271238</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.09047488002653929</v>
+      </c>
+      <c r="W45">
+        <v>0.2171945986496625</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3769786667772471</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.3630969132330647</v>
+      </c>
+      <c r="C46">
+        <v>31.25790588792415</v>
+      </c>
+      <c r="D46">
+        <v>59.68990588792414</v>
+      </c>
+      <c r="E46">
+        <v>-23.656</v>
+      </c>
+      <c r="F46">
+        <v>28.644</v>
+      </c>
+      <c r="G46">
+        <v>0.212</v>
+      </c>
+      <c r="H46">
+        <v>12.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>4.69</v>
+      </c>
+      <c r="K46">
+        <v>2.17</v>
+      </c>
+      <c r="L46">
+        <v>2.52</v>
+      </c>
+      <c r="M46">
+        <v>6.8401872</v>
+      </c>
+      <c r="N46">
+        <v>-4.320187199999999</v>
+      </c>
+      <c r="O46">
+        <v>-1.036844928</v>
+      </c>
+      <c r="P46">
+        <v>-3.283342272</v>
+      </c>
+      <c r="Q46">
+        <v>-1.113342271999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.4773486353816248</v>
+      </c>
+      <c r="T46">
+        <v>1.647065480901082</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.08841863275320885</v>
+      </c>
+      <c r="W46">
+        <v>0.2176856304985337</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.368410969805037</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.3650969132330646</v>
+      </c>
+      <c r="C47">
+        <v>30.24104336537379</v>
+      </c>
+      <c r="D47">
+        <v>59.32404336537378</v>
+      </c>
+      <c r="E47">
+        <v>-23.005</v>
+      </c>
+      <c r="F47">
+        <v>29.295</v>
+      </c>
+      <c r="G47">
+        <v>0.212</v>
+      </c>
+      <c r="H47">
+        <v>12.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>4.69</v>
+      </c>
+      <c r="K47">
+        <v>2.17</v>
+      </c>
+      <c r="L47">
+        <v>2.52</v>
+      </c>
+      <c r="M47">
+        <v>6.995646</v>
+      </c>
+      <c r="N47">
+        <v>-4.475645999999999</v>
+      </c>
+      <c r="O47">
+        <v>-1.07415504</v>
+      </c>
+      <c r="P47">
+        <v>-3.401490959999999</v>
+      </c>
+      <c r="Q47">
+        <v>-1.231490959999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.4853222469340178</v>
+      </c>
+      <c r="T47">
+        <v>1.677012126008374</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.08645377424758201</v>
+      </c>
+      <c r="W47">
+        <v>0.2181548387096774</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3602240593649251</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.3670969132330647</v>
+      </c>
+      <c r="C48">
+        <v>29.22863854568691</v>
+      </c>
+      <c r="D48">
+        <v>58.96263854568691</v>
+      </c>
+      <c r="E48">
+        <v>-22.354</v>
+      </c>
+      <c r="F48">
+        <v>29.946</v>
+      </c>
+      <c r="G48">
+        <v>0.212</v>
+      </c>
+      <c r="H48">
+        <v>12.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>4.69</v>
+      </c>
+      <c r="K48">
+        <v>2.17</v>
+      </c>
+      <c r="L48">
+        <v>2.52</v>
+      </c>
+      <c r="M48">
+        <v>7.1511048</v>
+      </c>
+      <c r="N48">
+        <v>-4.631104799999999</v>
+      </c>
+      <c r="O48">
+        <v>-1.111465152</v>
+      </c>
+      <c r="P48">
+        <v>-3.519639647999999</v>
+      </c>
+      <c r="Q48">
+        <v>-1.349639647999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.493591177432796</v>
+      </c>
+      <c r="T48">
+        <v>1.70806790611964</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.08457434437263456</v>
+      </c>
+      <c r="W48">
+        <v>0.2186036465638149</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3523931015526441</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.3690969132330647</v>
+      </c>
+      <c r="C49">
+        <v>28.22061045257797</v>
+      </c>
+      <c r="D49">
+        <v>58.60561045257796</v>
+      </c>
+      <c r="E49">
+        <v>-21.703</v>
+      </c>
+      <c r="F49">
+        <v>30.597</v>
+      </c>
+      <c r="G49">
+        <v>0.212</v>
+      </c>
+      <c r="H49">
+        <v>12.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>4.69</v>
+      </c>
+      <c r="K49">
+        <v>2.17</v>
+      </c>
+      <c r="L49">
+        <v>2.52</v>
+      </c>
+      <c r="M49">
+        <v>7.3065636</v>
+      </c>
+      <c r="N49">
+        <v>-4.786563599999999</v>
+      </c>
+      <c r="O49">
+        <v>-1.148775264</v>
+      </c>
+      <c r="P49">
+        <v>-3.637788335999999</v>
+      </c>
+      <c r="Q49">
+        <v>-1.467788335999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.5021721430447356</v>
+      </c>
+      <c r="T49">
+        <v>1.74029560246152</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.08277489023704659</v>
+      </c>
+      <c r="W49">
+        <v>0.2190333562113933</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3448953759876943</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.3710969132330647</v>
+      </c>
+      <c r="C50">
+        <v>27.21688005925365</v>
+      </c>
+      <c r="D50">
+        <v>58.25288005925365</v>
+      </c>
+      <c r="E50">
+        <v>-21.052</v>
+      </c>
+      <c r="F50">
+        <v>31.248</v>
+      </c>
+      <c r="G50">
+        <v>0.212</v>
+      </c>
+      <c r="H50">
+        <v>12.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>4.69</v>
+      </c>
+      <c r="K50">
+        <v>2.17</v>
+      </c>
+      <c r="L50">
+        <v>2.52</v>
+      </c>
+      <c r="M50">
+        <v>7.4620224</v>
+      </c>
+      <c r="N50">
+        <v>-4.942022399999999</v>
+      </c>
+      <c r="O50">
+        <v>-1.186085376</v>
+      </c>
+      <c r="P50">
+        <v>-3.755937024</v>
+      </c>
+      <c r="Q50">
+        <v>-1.585937023999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.5110831457955958</v>
+      </c>
+      <c r="T50">
+        <v>1.77376282558578</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.08105041335710812</v>
+      </c>
+      <c r="W50">
+        <v>0.2194451612903226</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3377100556546172</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.3730969132330647</v>
+      </c>
+      <c r="C51">
+        <v>26.21737023009683</v>
+      </c>
+      <c r="D51">
+        <v>57.90437023009682</v>
+      </c>
+      <c r="E51">
+        <v>-20.401</v>
+      </c>
+      <c r="F51">
+        <v>31.899</v>
+      </c>
+      <c r="G51">
+        <v>0.212</v>
+      </c>
+      <c r="H51">
+        <v>12.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>4.69</v>
+      </c>
+      <c r="K51">
+        <v>2.17</v>
+      </c>
+      <c r="L51">
+        <v>2.52</v>
+      </c>
+      <c r="M51">
+        <v>7.617481199999999</v>
+      </c>
+      <c r="N51">
+        <v>-5.097481199999999</v>
+      </c>
+      <c r="O51">
+        <v>-1.223395488</v>
+      </c>
+      <c r="P51">
+        <v>-3.874085711999999</v>
+      </c>
+      <c r="Q51">
+        <v>-1.704085711999999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.5203435996347252</v>
+      </c>
+      <c r="T51">
+        <v>1.80854248883256</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.07939632328859571</v>
+      </c>
+      <c r="W51">
+        <v>0.2198401579986834</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3308180137024822</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.3750969132330647</v>
+      </c>
+      <c r="C52">
+        <v>25.22200566443121</v>
+      </c>
+      <c r="D52">
+        <v>57.5600056644312</v>
+      </c>
+      <c r="E52">
+        <v>-19.75</v>
+      </c>
+      <c r="F52">
+        <v>32.55</v>
+      </c>
+      <c r="G52">
+        <v>0.212</v>
+      </c>
+      <c r="H52">
+        <v>12.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>4.69</v>
+      </c>
+      <c r="K52">
+        <v>2.17</v>
+      </c>
+      <c r="L52">
+        <v>2.52</v>
+      </c>
+      <c r="M52">
+        <v>7.772939999999999</v>
+      </c>
+      <c r="N52">
+        <v>-5.252939999999999</v>
+      </c>
+      <c r="O52">
+        <v>-1.2607056</v>
+      </c>
+      <c r="P52">
+        <v>-3.992234399999999</v>
+      </c>
+      <c r="Q52">
+        <v>-1.822234399999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.5299744716274197</v>
+      </c>
+      <c r="T52">
+        <v>1.844713338609211</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.0778083968228238</v>
+      </c>
+      <c r="W52">
+        <v>0.2202193548387097</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3242016534284325</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.3770969132330647</v>
+      </c>
+      <c r="C53">
+        <v>24.23071284228077</v>
+      </c>
+      <c r="D53">
+        <v>57.21971284228076</v>
+      </c>
+      <c r="E53">
+        <v>-19.099</v>
+      </c>
+      <c r="F53">
+        <v>33.201</v>
+      </c>
+      <c r="G53">
+        <v>0.212</v>
+      </c>
+      <c r="H53">
+        <v>12.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>4.69</v>
+      </c>
+      <c r="K53">
+        <v>2.17</v>
+      </c>
+      <c r="L53">
+        <v>2.52</v>
+      </c>
+      <c r="M53">
+        <v>7.928398800000001</v>
+      </c>
+      <c r="N53">
+        <v>-5.408398800000001</v>
+      </c>
+      <c r="O53">
+        <v>-1.298015712</v>
+      </c>
+      <c r="P53">
+        <v>-4.110383088000001</v>
+      </c>
+      <c r="Q53">
+        <v>-1.940383088</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.5399984404361426</v>
+      </c>
+      <c r="T53">
+        <v>1.882360549601236</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.07628274198316057</v>
+      </c>
+      <c r="W53">
+        <v>0.2205836812144213</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3178447582631692</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.3790969132330647</v>
+      </c>
+      <c r="C54">
+        <v>23.24341997204193</v>
+      </c>
+      <c r="D54">
+        <v>56.88341997204193</v>
+      </c>
+      <c r="E54">
+        <v>-18.448</v>
+      </c>
+      <c r="F54">
+        <v>33.852</v>
+      </c>
+      <c r="G54">
+        <v>0.212</v>
+      </c>
+      <c r="H54">
+        <v>12.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>4.69</v>
+      </c>
+      <c r="K54">
+        <v>2.17</v>
+      </c>
+      <c r="L54">
+        <v>2.52</v>
+      </c>
+      <c r="M54">
+        <v>8.0838576</v>
+      </c>
+      <c r="N54">
+        <v>-5.5638576</v>
+      </c>
+      <c r="O54">
+        <v>-1.335325824</v>
+      </c>
+      <c r="P54">
+        <v>-4.228531776000001</v>
+      </c>
+      <c r="Q54">
+        <v>-2.058531776</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.5504400746118956</v>
+      </c>
+      <c r="T54">
+        <v>1.921576394384595</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.07481576617579211</v>
+      </c>
+      <c r="W54">
+        <v>0.2209339950372209</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3117323590658004</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.3810969132330647</v>
+      </c>
+      <c r="C55">
+        <v>22.26005693999023</v>
+      </c>
+      <c r="D55">
+        <v>56.55105693999023</v>
+      </c>
+      <c r="E55">
+        <v>-17.797</v>
+      </c>
+      <c r="F55">
+        <v>34.503</v>
+      </c>
+      <c r="G55">
+        <v>0.212</v>
+      </c>
+      <c r="H55">
+        <v>12.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>4.69</v>
+      </c>
+      <c r="K55">
+        <v>2.17</v>
+      </c>
+      <c r="L55">
+        <v>2.52</v>
+      </c>
+      <c r="M55">
+        <v>8.2393164</v>
+      </c>
+      <c r="N55">
+        <v>-5.7193164</v>
+      </c>
+      <c r="O55">
+        <v>-1.372635936</v>
+      </c>
+      <c r="P55">
+        <v>-4.346680464</v>
+      </c>
+      <c r="Q55">
+        <v>-2.176680464</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.5613260336461912</v>
+      </c>
+      <c r="T55">
+        <v>1.962460998520438</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.07340414794606019</v>
+      </c>
+      <c r="W55">
+        <v>0.2212710894704808</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3058506164419174</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.3830969132330647</v>
+      </c>
+      <c r="C56">
+        <v>21.28055526154672</v>
+      </c>
+      <c r="D56">
+        <v>56.22255526154672</v>
+      </c>
+      <c r="E56">
+        <v>-17.146</v>
+      </c>
+      <c r="F56">
+        <v>35.154</v>
+      </c>
+      <c r="G56">
+        <v>0.212</v>
+      </c>
+      <c r="H56">
+        <v>12.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>4.69</v>
+      </c>
+      <c r="K56">
+        <v>2.17</v>
+      </c>
+      <c r="L56">
+        <v>2.52</v>
+      </c>
+      <c r="M56">
+        <v>8.3947752</v>
+      </c>
+      <c r="N56">
+        <v>-5.8747752</v>
+      </c>
+      <c r="O56">
+        <v>-1.409946048</v>
+      </c>
+      <c r="P56">
+        <v>-4.464829152</v>
+      </c>
+      <c r="Q56">
+        <v>-2.294829152</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.5726852952471952</v>
+      </c>
+      <c r="T56">
+        <v>2.005123194140447</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.07204481187298499</v>
+      </c>
+      <c r="W56">
+        <v>0.2215956989247312</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3001867161374374</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.3850969132330647</v>
+      </c>
+      <c r="C57">
+        <v>20.30484803423332</v>
+      </c>
+      <c r="D57">
+        <v>55.89784803423331</v>
+      </c>
+      <c r="E57">
+        <v>-16.495</v>
+      </c>
+      <c r="F57">
+        <v>35.805</v>
+      </c>
+      <c r="G57">
+        <v>0.212</v>
+      </c>
+      <c r="H57">
+        <v>12.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>4.69</v>
+      </c>
+      <c r="K57">
+        <v>2.17</v>
+      </c>
+      <c r="L57">
+        <v>2.52</v>
+      </c>
+      <c r="M57">
+        <v>8.550234</v>
+      </c>
+      <c r="N57">
+        <v>-6.030234</v>
+      </c>
+      <c r="O57">
+        <v>-1.44725616</v>
+      </c>
+      <c r="P57">
+        <v>-4.58297784</v>
+      </c>
+      <c r="Q57">
+        <v>-2.412977839999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.5845494129193554</v>
+      </c>
+      <c r="T57">
+        <v>2.049681487343569</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.07073490620256709</v>
+      </c>
+      <c r="W57">
+        <v>0.221908504398827</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2947287758440295</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.3870969132330647</v>
+      </c>
+      <c r="C58">
+        <v>19.33286989224889</v>
+      </c>
+      <c r="D58">
+        <v>55.57686989224889</v>
+      </c>
+      <c r="E58">
+        <v>-15.84399999999999</v>
+      </c>
+      <c r="F58">
+        <v>36.456</v>
+      </c>
+      <c r="G58">
+        <v>0.212</v>
+      </c>
+      <c r="H58">
+        <v>12.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>4.69</v>
+      </c>
+      <c r="K58">
+        <v>2.17</v>
+      </c>
+      <c r="L58">
+        <v>2.52</v>
+      </c>
+      <c r="M58">
+        <v>8.705692800000001</v>
+      </c>
+      <c r="N58">
+        <v>-6.185692800000002</v>
+      </c>
+      <c r="O58">
+        <v>-1.484566272</v>
+      </c>
+      <c r="P58">
+        <v>-4.701126528000001</v>
+      </c>
+      <c r="Q58">
+        <v>-2.531126528000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.5969528086675224</v>
+      </c>
+      <c r="T58">
+        <v>2.096265157510468</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.06947178287752123</v>
+      </c>
+      <c r="W58">
+        <v>0.2222101382488479</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2894657619896718</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.3890969132330647</v>
+      </c>
+      <c r="C59">
+        <v>18.36455696260127</v>
+      </c>
+      <c r="D59">
+        <v>55.25955696260127</v>
+      </c>
+      <c r="E59">
+        <v>-15.193</v>
+      </c>
+      <c r="F59">
+        <v>37.107</v>
+      </c>
+      <c r="G59">
+        <v>0.212</v>
+      </c>
+      <c r="H59">
+        <v>12.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>4.69</v>
+      </c>
+      <c r="K59">
+        <v>2.17</v>
+      </c>
+      <c r="L59">
+        <v>2.52</v>
+      </c>
+      <c r="M59">
+        <v>8.861151599999999</v>
+      </c>
+      <c r="N59">
+        <v>-6.3411516</v>
+      </c>
+      <c r="O59">
+        <v>-1.521876384</v>
+      </c>
+      <c r="P59">
+        <v>-4.819275215999999</v>
+      </c>
+      <c r="Q59">
+        <v>-2.649275215999999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.6099331065435114</v>
+      </c>
+      <c r="T59">
+        <v>2.145015510010711</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.06825297966914368</v>
+      </c>
+      <c r="W59">
+        <v>0.2225011884550085</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2843874152880986</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.3910969132330646</v>
+      </c>
+      <c r="C60">
+        <v>17.39984682273388</v>
+      </c>
+      <c r="D60">
+        <v>54.94584682273387</v>
+      </c>
+      <c r="E60">
+        <v>-14.542</v>
+      </c>
+      <c r="F60">
+        <v>37.758</v>
+      </c>
+      <c r="G60">
+        <v>0.212</v>
+      </c>
+      <c r="H60">
+        <v>12.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>4.69</v>
+      </c>
+      <c r="K60">
+        <v>2.17</v>
+      </c>
+      <c r="L60">
+        <v>2.52</v>
+      </c>
+      <c r="M60">
+        <v>9.016610399999999</v>
+      </c>
+      <c r="N60">
+        <v>-6.4966104</v>
+      </c>
+      <c r="O60">
+        <v>-1.559186496</v>
+      </c>
+      <c r="P60">
+        <v>-4.937423904</v>
+      </c>
+      <c r="Q60">
+        <v>-2.767423904</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.6235315138421662</v>
+      </c>
+      <c r="T60">
+        <v>2.196087307868109</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.06707620415760672</v>
+      </c>
+      <c r="W60">
+        <v>0.2227822024471635</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2794841839900279</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.3930969132330647</v>
+      </c>
+      <c r="C61">
+        <v>16.43867845958706</v>
+      </c>
+      <c r="D61">
+        <v>54.63567845958705</v>
+      </c>
+      <c r="E61">
+        <v>-13.89100000000001</v>
+      </c>
+      <c r="F61">
+        <v>38.40899999999999</v>
+      </c>
+      <c r="G61">
+        <v>0.212</v>
+      </c>
+      <c r="H61">
+        <v>12.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>4.69</v>
+      </c>
+      <c r="K61">
+        <v>2.17</v>
+      </c>
+      <c r="L61">
+        <v>2.52</v>
+      </c>
+      <c r="M61">
+        <v>9.172069199999999</v>
+      </c>
+      <c r="N61">
+        <v>-6.6520692</v>
+      </c>
+      <c r="O61">
+        <v>-1.596496608</v>
+      </c>
+      <c r="P61">
+        <v>-5.055572592</v>
+      </c>
+      <c r="Q61">
+        <v>-2.885572591999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.637793258082219</v>
+      </c>
+      <c r="T61">
+        <v>2.249650412938062</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.0659393193413761</v>
+      </c>
+      <c r="W61">
+        <v>0.2230536905412794</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2747471639224004</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.3950969132330647</v>
+      </c>
+      <c r="C62">
+        <v>15.48099223003867</v>
+      </c>
+      <c r="D62">
+        <v>54.32899223003866</v>
+      </c>
+      <c r="E62">
+        <v>-13.24</v>
+      </c>
+      <c r="F62">
+        <v>39.06</v>
+      </c>
+      <c r="G62">
+        <v>0.212</v>
+      </c>
+      <c r="H62">
+        <v>12.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>4.69</v>
+      </c>
+      <c r="K62">
+        <v>2.17</v>
+      </c>
+      <c r="L62">
+        <v>2.52</v>
+      </c>
+      <c r="M62">
+        <v>9.327527999999999</v>
+      </c>
+      <c r="N62">
+        <v>-6.807528</v>
+      </c>
+      <c r="O62">
+        <v>-1.63380672</v>
+      </c>
+      <c r="P62">
+        <v>-5.17372128</v>
+      </c>
+      <c r="Q62">
+        <v>-3.003721279999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.6527680895342747</v>
+      </c>
+      <c r="T62">
+        <v>2.305891673261514</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.0648403306856865</v>
+      </c>
+      <c r="W62">
+        <v>0.2233161290322581</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2701680445236937</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.3970969132330648</v>
+      </c>
+      <c r="C63">
+        <v>14.52672982266928</v>
+      </c>
+      <c r="D63">
+        <v>54.02572982266928</v>
+      </c>
+      <c r="E63">
+        <v>-12.589</v>
+      </c>
+      <c r="F63">
+        <v>39.711</v>
+      </c>
+      <c r="G63">
+        <v>0.212</v>
+      </c>
+      <c r="H63">
+        <v>12.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>4.69</v>
+      </c>
+      <c r="K63">
+        <v>2.17</v>
+      </c>
+      <c r="L63">
+        <v>2.52</v>
+      </c>
+      <c r="M63">
+        <v>9.482986800000001</v>
+      </c>
+      <c r="N63">
+        <v>-6.962986800000001</v>
+      </c>
+      <c r="O63">
+        <v>-1.671116832</v>
+      </c>
+      <c r="P63">
+        <v>-5.291869968000001</v>
+      </c>
+      <c r="Q63">
+        <v>-3.121869968000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.6685108610607946</v>
+      </c>
+      <c r="T63">
+        <v>2.36501710078104</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.06377737444493753</v>
+      </c>
+      <c r="W63">
+        <v>0.2235699629825489</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2657390601872397</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.3990969132330647</v>
+      </c>
+      <c r="C64">
+        <v>13.57583422080094</v>
+      </c>
+      <c r="D64">
+        <v>53.72583422080093</v>
+      </c>
+      <c r="E64">
+        <v>-11.938</v>
+      </c>
+      <c r="F64">
+        <v>40.36199999999999</v>
+      </c>
+      <c r="G64">
+        <v>0.212</v>
+      </c>
+      <c r="H64">
+        <v>12.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>4.69</v>
+      </c>
+      <c r="K64">
+        <v>2.17</v>
+      </c>
+      <c r="L64">
+        <v>2.52</v>
+      </c>
+      <c r="M64">
+        <v>9.638445599999999</v>
+      </c>
+      <c r="N64">
+        <v>-7.118445599999999</v>
+      </c>
+      <c r="O64">
+        <v>-1.708426944</v>
+      </c>
+      <c r="P64">
+        <v>-5.410018656</v>
+      </c>
+      <c r="Q64">
+        <v>-3.240018656</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.6850821995097627</v>
+      </c>
+      <c r="T64">
+        <v>2.427254392906857</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.06274870711518049</v>
+      </c>
+      <c r="W64">
+        <v>0.2238156087408949</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.261452946313252</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.4010969132330647</v>
+      </c>
+      <c r="C65">
+        <v>12.62824966676009</v>
+      </c>
+      <c r="D65">
+        <v>53.42924966676009</v>
+      </c>
+      <c r="E65">
+        <v>-11.287</v>
+      </c>
+      <c r="F65">
+        <v>41.013</v>
+      </c>
+      <c r="G65">
+        <v>0.212</v>
+      </c>
+      <c r="H65">
+        <v>12.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>4.69</v>
+      </c>
+      <c r="K65">
+        <v>2.17</v>
+      </c>
+      <c r="L65">
+        <v>2.52</v>
+      </c>
+      <c r="M65">
+        <v>9.793904400000001</v>
+      </c>
+      <c r="N65">
+        <v>-7.273904400000001</v>
+      </c>
+      <c r="O65">
+        <v>-1.745737056</v>
+      </c>
+      <c r="P65">
+        <v>-5.528167344000001</v>
+      </c>
+      <c r="Q65">
+        <v>-3.358167344</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.7025492859829996</v>
+      </c>
+      <c r="T65">
+        <v>2.492855862985421</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.06175269589112999</v>
+      </c>
+      <c r="W65">
+        <v>0.2240534562211982</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.257302899546375</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.4030969132330647</v>
+      </c>
+      <c r="C66">
+        <v>11.68392162731786</v>
+      </c>
+      <c r="D66">
+        <v>53.13592162731785</v>
+      </c>
+      <c r="E66">
+        <v>-10.636</v>
+      </c>
+      <c r="F66">
+        <v>41.66399999999999</v>
+      </c>
+      <c r="G66">
+        <v>0.212</v>
+      </c>
+      <c r="H66">
+        <v>12.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>4.69</v>
+      </c>
+      <c r="K66">
+        <v>2.17</v>
+      </c>
+      <c r="L66">
+        <v>2.52</v>
+      </c>
+      <c r="M66">
+        <v>9.949363199999999</v>
+      </c>
+      <c r="N66">
+        <v>-7.429363199999999</v>
+      </c>
+      <c r="O66">
+        <v>-1.783047168</v>
+      </c>
+      <c r="P66">
+        <v>-5.646316032</v>
+      </c>
+      <c r="Q66">
+        <v>-3.476316031999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.720986766149194</v>
+      </c>
+      <c r="T66">
+        <v>2.56210185917946</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.0607878100178311</v>
+      </c>
+      <c r="W66">
+        <v>0.224283870967742</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2532825417409629</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.4050969132330646</v>
+      </c>
+      <c r="C67">
+        <v>10.74279676026221</v>
+      </c>
+      <c r="D67">
+        <v>52.8457967602622</v>
+      </c>
+      <c r="E67">
+        <v>-9.984999999999999</v>
+      </c>
+      <c r="F67">
+        <v>42.315</v>
+      </c>
+      <c r="G67">
+        <v>0.212</v>
+      </c>
+      <c r="H67">
+        <v>12.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>4.69</v>
+      </c>
+      <c r="K67">
+        <v>2.17</v>
+      </c>
+      <c r="L67">
+        <v>2.52</v>
+      </c>
+      <c r="M67">
+        <v>10.104822</v>
+      </c>
+      <c r="N67">
+        <v>-7.584822000000001</v>
+      </c>
+      <c r="O67">
+        <v>-1.82035728</v>
+      </c>
+      <c r="P67">
+        <v>-5.764464720000001</v>
+      </c>
+      <c r="Q67">
+        <v>-3.594464720000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.7404778166105994</v>
+      </c>
+      <c r="T67">
+        <v>2.63530476944173</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.05985261294063368</v>
+      </c>
+      <c r="W67">
+        <v>0.2245071960297767</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2493858872526403</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.4070969132330646</v>
+      </c>
+      <c r="C68">
+        <v>9.804822882059646</v>
+      </c>
+      <c r="D68">
+        <v>52.55882288205964</v>
+      </c>
+      <c r="E68">
+        <v>-9.333999999999996</v>
+      </c>
+      <c r="F68">
+        <v>42.966</v>
+      </c>
+      <c r="G68">
+        <v>0.212</v>
+      </c>
+      <c r="H68">
+        <v>12.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>4.69</v>
+      </c>
+      <c r="K68">
+        <v>2.17</v>
+      </c>
+      <c r="L68">
+        <v>2.52</v>
+      </c>
+      <c r="M68">
+        <v>10.2602808</v>
+      </c>
+      <c r="N68">
+        <v>-7.740280800000001</v>
+      </c>
+      <c r="O68">
+        <v>-1.857667392</v>
+      </c>
+      <c r="P68">
+        <v>-5.882613408000001</v>
+      </c>
+      <c r="Q68">
+        <v>-3.712613408000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.7611153994520876</v>
+      </c>
+      <c r="T68">
+        <v>2.71281373324884</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0589457551688059</v>
+      </c>
+      <c r="W68">
+        <v>0.2247237536656891</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2456073132033579</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.4090969132330647</v>
+      </c>
+      <c r="C69">
+        <v>8.869948936564555</v>
+      </c>
+      <c r="D69">
+        <v>52.27494893656455</v>
+      </c>
+      <c r="E69">
+        <v>-8.683</v>
+      </c>
+      <c r="F69">
+        <v>43.617</v>
+      </c>
+      <c r="G69">
+        <v>0.212</v>
+      </c>
+      <c r="H69">
+        <v>12.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>4.69</v>
+      </c>
+      <c r="K69">
+        <v>2.17</v>
+      </c>
+      <c r="L69">
+        <v>2.52</v>
+      </c>
+      <c r="M69">
+        <v>10.4157396</v>
+      </c>
+      <c r="N69">
+        <v>-7.895739600000001</v>
+      </c>
+      <c r="O69">
+        <v>-1.894977504</v>
+      </c>
+      <c r="P69">
+        <v>-6.000762096000001</v>
+      </c>
+      <c r="Q69">
+        <v>-3.830762096</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.78300374489003</v>
+      </c>
+      <c r="T69">
+        <v>2.795020210013957</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.05806596777822671</v>
+      </c>
+      <c r="W69">
+        <v>0.2249338468945595</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.241941532409278</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.4110969132330647</v>
+      </c>
+      <c r="C70">
+        <v>7.938124964737312</v>
+      </c>
+      <c r="D70">
+        <v>51.99412496473731</v>
+      </c>
+      <c r="E70">
+        <v>-8.031999999999996</v>
+      </c>
+      <c r="F70">
+        <v>44.268</v>
+      </c>
+      <c r="G70">
+        <v>0.212</v>
+      </c>
+      <c r="H70">
+        <v>12.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>4.69</v>
+      </c>
+      <c r="K70">
+        <v>2.17</v>
+      </c>
+      <c r="L70">
+        <v>2.52</v>
+      </c>
+      <c r="M70">
+        <v>10.5711984</v>
+      </c>
+      <c r="N70">
+        <v>-8.051198400000001</v>
+      </c>
+      <c r="O70">
+        <v>-1.932287616</v>
+      </c>
+      <c r="P70">
+        <v>-6.118910784000001</v>
+      </c>
+      <c r="Q70">
+        <v>-3.948910784</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.8062601119178434</v>
+      </c>
+      <c r="T70">
+        <v>2.882364591576894</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.05721205648737043</v>
+      </c>
+      <c r="W70">
+        <v>0.225137760910816</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2383835686973768</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.4130969132330646</v>
+      </c>
+      <c r="C71">
+        <v>7.00930207533316</v>
+      </c>
+      <c r="D71">
+        <v>51.71630207533315</v>
+      </c>
+      <c r="E71">
+        <v>-7.381</v>
+      </c>
+      <c r="F71">
+        <v>44.919</v>
+      </c>
+      <c r="G71">
+        <v>0.212</v>
+      </c>
+      <c r="H71">
+        <v>12.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>4.69</v>
+      </c>
+      <c r="K71">
+        <v>2.17</v>
+      </c>
+      <c r="L71">
+        <v>2.52</v>
+      </c>
+      <c r="M71">
+        <v>10.7266572</v>
+      </c>
+      <c r="N71">
+        <v>-8.2066572</v>
+      </c>
+      <c r="O71">
+        <v>-1.969597728</v>
+      </c>
+      <c r="P71">
+        <v>-6.237059472</v>
+      </c>
+      <c r="Q71">
+        <v>-4.067059472</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.8310168897216448</v>
+      </c>
+      <c r="T71">
+        <v>2.975344094530987</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.05638289624842304</v>
+      </c>
+      <c r="W71">
+        <v>0.2253357643758766</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2349287343684293</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.4150969132330647</v>
+      </c>
+      <c r="C72">
+        <v>6.083432416525703</v>
+      </c>
+      <c r="D72">
+        <v>51.4414324165257</v>
+      </c>
+      <c r="E72">
+        <v>-6.729999999999997</v>
+      </c>
+      <c r="F72">
+        <v>45.57</v>
+      </c>
+      <c r="G72">
+        <v>0.212</v>
+      </c>
+      <c r="H72">
+        <v>12.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>4.69</v>
+      </c>
+      <c r="K72">
+        <v>2.17</v>
+      </c>
+      <c r="L72">
+        <v>2.52</v>
+      </c>
+      <c r="M72">
+        <v>10.882116</v>
+      </c>
+      <c r="N72">
+        <v>-8.362116</v>
+      </c>
+      <c r="O72">
+        <v>-2.00690784</v>
+      </c>
+      <c r="P72">
+        <v>-6.35520816</v>
+      </c>
+      <c r="Q72">
+        <v>-4.18520816</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.8574241193790328</v>
+      </c>
+      <c r="T72">
+        <v>3.074522231015353</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.055577426302017</v>
+      </c>
+      <c r="W72">
+        <v>0.2255281105990783</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2315726095917374</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.4170969132330647</v>
+      </c>
+      <c r="C73">
+        <v>5.16046914843087</v>
+      </c>
+      <c r="D73">
+        <v>51.16946914843086</v>
+      </c>
+      <c r="E73">
+        <v>-6.079000000000001</v>
+      </c>
+      <c r="F73">
+        <v>46.221</v>
+      </c>
+      <c r="G73">
+        <v>0.212</v>
+      </c>
+      <c r="H73">
+        <v>12.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>4.69</v>
+      </c>
+      <c r="K73">
+        <v>2.17</v>
+      </c>
+      <c r="L73">
+        <v>2.52</v>
+      </c>
+      <c r="M73">
+        <v>11.0375748</v>
+      </c>
+      <c r="N73">
+        <v>-8.5175748</v>
+      </c>
+      <c r="O73">
+        <v>-2.044217952</v>
+      </c>
+      <c r="P73">
+        <v>-6.473356848</v>
+      </c>
+      <c r="Q73">
+        <v>-4.303356848</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.8856525372886546</v>
+      </c>
+      <c r="T73">
+        <v>3.180540238981399</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.05479464564987591</v>
+      </c>
+      <c r="W73">
+        <v>0.2257150386188096</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2283110235411496</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.4190969132330646</v>
+      </c>
+      <c r="C74">
+        <v>4.24036641649748</v>
+      </c>
+      <c r="D74">
+        <v>50.90036641649747</v>
+      </c>
+      <c r="E74">
+        <v>-5.428000000000004</v>
+      </c>
+      <c r="F74">
+        <v>46.87199999999999</v>
+      </c>
+      <c r="G74">
+        <v>0.212</v>
+      </c>
+      <c r="H74">
+        <v>12.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>4.69</v>
+      </c>
+      <c r="K74">
+        <v>2.17</v>
+      </c>
+      <c r="L74">
+        <v>2.52</v>
+      </c>
+      <c r="M74">
+        <v>11.1930336</v>
+      </c>
+      <c r="N74">
+        <v>-8.6730336</v>
+      </c>
+      <c r="O74">
+        <v>-2.081528064</v>
+      </c>
+      <c r="P74">
+        <v>-6.591505536</v>
+      </c>
+      <c r="Q74">
+        <v>-4.421505536</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.9158972707632493</v>
+      </c>
+      <c r="T74">
+        <v>3.294130961802163</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.05403360890473875</v>
+      </c>
+      <c r="W74">
+        <v>0.2258967741935484</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2251400371030781</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.4210969132330648</v>
+      </c>
+      <c r="C75">
+        <v>3.323079325733183</v>
+      </c>
+      <c r="D75">
+        <v>50.63407932573318</v>
+      </c>
+      <c r="E75">
+        <v>-4.777000000000001</v>
+      </c>
+      <c r="F75">
+        <v>47.523</v>
+      </c>
+      <c r="G75">
+        <v>0.212</v>
+      </c>
+      <c r="H75">
+        <v>12.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>4.69</v>
+      </c>
+      <c r="K75">
+        <v>2.17</v>
+      </c>
+      <c r="L75">
+        <v>2.52</v>
+      </c>
+      <c r="M75">
+        <v>11.3484924</v>
+      </c>
+      <c r="N75">
+        <v>-8.8284924</v>
+      </c>
+      <c r="O75">
+        <v>-2.118838176</v>
+      </c>
+      <c r="P75">
+        <v>-6.709654223999999</v>
+      </c>
+      <c r="Q75">
+        <v>-4.539654224</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.9483823548655921</v>
+      </c>
+      <c r="T75">
+        <v>3.41613581223928</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.05329342248138616</v>
+      </c>
+      <c r="W75">
+        <v>0.226073530711445</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2220559270057757</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.4230969132330646</v>
+      </c>
+      <c r="C76">
+        <v>2.408563915735485</v>
+      </c>
+      <c r="D76">
+        <v>50.37056391573547</v>
+      </c>
+      <c r="E76">
+        <v>-4.126000000000005</v>
+      </c>
+      <c r="F76">
+        <v>48.17399999999999</v>
+      </c>
+      <c r="G76">
+        <v>0.212</v>
+      </c>
+      <c r="H76">
+        <v>12.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>4.69</v>
+      </c>
+      <c r="K76">
+        <v>2.17</v>
+      </c>
+      <c r="L76">
+        <v>2.52</v>
+      </c>
+      <c r="M76">
+        <v>11.5039512</v>
+      </c>
+      <c r="N76">
+        <v>-8.9839512</v>
+      </c>
+      <c r="O76">
+        <v>-2.156148288</v>
+      </c>
+      <c r="P76">
+        <v>-6.827802912</v>
+      </c>
+      <c r="Q76">
+        <v>-4.657802911999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.9833662915911916</v>
+      </c>
+      <c r="T76">
+        <v>3.54752565117156</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.05257324109650256</v>
+      </c>
+      <c r="W76">
+        <v>0.2262455100261552</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2190551712354273</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.4250969132330646</v>
+      </c>
+      <c r="C77">
+        <v>1.496777136497897</v>
+      </c>
+      <c r="D77">
+        <v>50.10977713649789</v>
+      </c>
+      <c r="E77">
+        <v>-3.475000000000001</v>
+      </c>
+      <c r="F77">
+        <v>48.825</v>
+      </c>
+      <c r="G77">
+        <v>0.212</v>
+      </c>
+      <c r="H77">
+        <v>12.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>4.69</v>
+      </c>
+      <c r="K77">
+        <v>2.17</v>
+      </c>
+      <c r="L77">
+        <v>2.52</v>
+      </c>
+      <c r="M77">
+        <v>11.65941</v>
+      </c>
+      <c r="N77">
+        <v>-9.13941</v>
+      </c>
+      <c r="O77">
+        <v>-2.1934584</v>
+      </c>
+      <c r="P77">
+        <v>-6.9459516</v>
+      </c>
+      <c r="Q77">
+        <v>-4.775951599999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>1.021148943254839</v>
+      </c>
+      <c r="T77">
+        <v>3.689426677218423</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.0518722645485492</v>
+      </c>
+      <c r="W77">
+        <v>0.2264129032258065</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.216134435618955</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.4270969132330646</v>
+      </c>
+      <c r="C78">
+        <v>0.5876768249642836</v>
+      </c>
+      <c r="D78">
+        <v>49.85167682496428</v>
+      </c>
+      <c r="E78">
+        <v>-2.823999999999998</v>
+      </c>
+      <c r="F78">
+        <v>49.476</v>
+      </c>
+      <c r="G78">
+        <v>0.212</v>
+      </c>
+      <c r="H78">
+        <v>12.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>4.69</v>
+      </c>
+      <c r="K78">
+        <v>2.17</v>
+      </c>
+      <c r="L78">
+        <v>2.52</v>
+      </c>
+      <c r="M78">
+        <v>11.8148688</v>
+      </c>
+      <c r="N78">
+        <v>-9.294868800000001</v>
+      </c>
+      <c r="O78">
+        <v>-2.230768512</v>
+      </c>
+      <c r="P78">
+        <v>-7.064100288000001</v>
+      </c>
+      <c r="Q78">
+        <v>-4.894100288000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>1.062080149223791</v>
+      </c>
+      <c r="T78">
+        <v>3.84315278876919</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.05118973475185775</v>
+      </c>
+      <c r="W78">
+        <v>0.2265758913412564</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2132905614660739</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.4290969132330646</v>
+      </c>
+      <c r="C79">
+        <v>-0.3187783176962782</v>
+      </c>
+      <c r="D79">
+        <v>49.59622168230371</v>
+      </c>
+      <c r="E79">
+        <v>-2.173000000000002</v>
+      </c>
+      <c r="F79">
+        <v>50.127</v>
+      </c>
+      <c r="G79">
+        <v>0.212</v>
+      </c>
+      <c r="H79">
+        <v>12.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>4.69</v>
+      </c>
+      <c r="K79">
+        <v>2.17</v>
+      </c>
+      <c r="L79">
+        <v>2.52</v>
+      </c>
+      <c r="M79">
+        <v>11.9703276</v>
+      </c>
+      <c r="N79">
+        <v>-9.4503276</v>
+      </c>
+      <c r="O79">
+        <v>-2.268078624</v>
+      </c>
+      <c r="P79">
+        <v>-7.182248976</v>
+      </c>
+      <c r="Q79">
+        <v>-5.012248976</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>1.106570590494391</v>
+      </c>
+      <c r="T79">
+        <v>4.010246388280894</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05052493300183363</v>
+      </c>
+      <c r="W79">
+        <v>0.2267346459991622</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2105205541743068</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.4310969132330646</v>
+      </c>
+      <c r="C80">
+        <v>-1.222628748119313</v>
+      </c>
+      <c r="D80">
+        <v>49.34337125188068</v>
+      </c>
+      <c r="E80">
+        <v>-1.521999999999998</v>
+      </c>
+      <c r="F80">
+        <v>50.778</v>
+      </c>
+      <c r="G80">
+        <v>0.212</v>
+      </c>
+      <c r="H80">
+        <v>12.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>4.69</v>
+      </c>
+      <c r="K80">
+        <v>2.17</v>
+      </c>
+      <c r="L80">
+        <v>2.52</v>
+      </c>
+      <c r="M80">
+        <v>12.1257864</v>
+      </c>
+      <c r="N80">
+        <v>-9.605786400000001</v>
+      </c>
+      <c r="O80">
+        <v>-2.305388736</v>
+      </c>
+      <c r="P80">
+        <v>-7.300397664000001</v>
+      </c>
+      <c r="Q80">
+        <v>-5.130397664</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>1.155105617335045</v>
+      </c>
+      <c r="T80">
+        <v>4.192530315020935</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04987717745052807</v>
+      </c>
+      <c r="W80">
+        <v>0.2268893300248139</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2078215727105336</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.4330969132330648</v>
+      </c>
+      <c r="C81">
+        <v>-2.123914102104408</v>
+      </c>
+      <c r="D81">
+        <v>49.09308589789558</v>
+      </c>
+      <c r="E81">
+        <v>-0.8710000000000022</v>
+      </c>
+      <c r="F81">
+        <v>51.42899999999999</v>
+      </c>
+      <c r="G81">
+        <v>0.212</v>
+      </c>
+      <c r="H81">
+        <v>12.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>4.69</v>
+      </c>
+      <c r="K81">
+        <v>2.17</v>
+      </c>
+      <c r="L81">
+        <v>2.52</v>
+      </c>
+      <c r="M81">
+        <v>12.2812452</v>
+      </c>
+      <c r="N81">
+        <v>-9.761245199999999</v>
+      </c>
+      <c r="O81">
+        <v>-2.342698848</v>
+      </c>
+      <c r="P81">
+        <v>-7.418546352</v>
+      </c>
+      <c r="Q81">
+        <v>-5.248546352</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>1.208263027684333</v>
+      </c>
+      <c r="T81">
+        <v>4.392174615736219</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04924582077393911</v>
+      </c>
+      <c r="W81">
+        <v>0.2270400979991833</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2051909198914129</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.4350969132330647</v>
+      </c>
+      <c r="C82">
+        <v>-3.022673215327785</v>
+      </c>
+      <c r="D82">
+        <v>48.84532678467221</v>
+      </c>
+      <c r="E82">
+        <v>-0.2199999999999989</v>
+      </c>
+      <c r="F82">
+        <v>52.08</v>
+      </c>
+      <c r="G82">
+        <v>0.212</v>
+      </c>
+      <c r="H82">
+        <v>12.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>4.69</v>
+      </c>
+      <c r="K82">
+        <v>2.17</v>
+      </c>
+      <c r="L82">
+        <v>2.52</v>
+      </c>
+      <c r="M82">
+        <v>12.436704</v>
+      </c>
+      <c r="N82">
+        <v>-9.916704000000001</v>
+      </c>
+      <c r="O82">
+        <v>-2.38000896</v>
+      </c>
+      <c r="P82">
+        <v>-7.536695040000001</v>
+      </c>
+      <c r="Q82">
+        <v>-5.366695040000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>1.266736179068549</v>
+      </c>
+      <c r="T82">
+        <v>4.61178334652303</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04863024801426487</v>
+      </c>
+      <c r="W82">
+        <v>0.2271870967741936</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2026260333927703</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.4370969132330647</v>
+      </c>
+      <c r="C83">
+        <v>-3.918944143431062</v>
+      </c>
+      <c r="D83">
+        <v>48.60005585656894</v>
+      </c>
+      <c r="E83">
+        <v>0.4310000000000045</v>
+      </c>
+      <c r="F83">
+        <v>52.731</v>
+      </c>
+      <c r="G83">
+        <v>0.212</v>
+      </c>
+      <c r="H83">
+        <v>12.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>4.69</v>
+      </c>
+      <c r="K83">
+        <v>2.17</v>
+      </c>
+      <c r="L83">
+        <v>2.52</v>
+      </c>
+      <c r="M83">
+        <v>12.5921628</v>
+      </c>
+      <c r="N83">
+        <v>-10.0721628</v>
+      </c>
+      <c r="O83">
+        <v>-2.417319072</v>
+      </c>
+      <c r="P83">
+        <v>-7.654843728000001</v>
+      </c>
+      <c r="Q83">
+        <v>-5.484843728000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>1.331364399019526</v>
+      </c>
+      <c r="T83">
+        <v>4.854508785813715</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04802987458198999</v>
+      </c>
+      <c r="W83">
+        <v>0.2273304659498208</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2001244774249583</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.4390969132330647</v>
+      </c>
+      <c r="C84">
+        <v>-4.812764181507504</v>
+      </c>
+      <c r="D84">
+        <v>48.35723581849249</v>
+      </c>
+      <c r="E84">
+        <v>1.082000000000001</v>
+      </c>
+      <c r="F84">
+        <v>53.382</v>
+      </c>
+      <c r="G84">
+        <v>0.212</v>
+      </c>
+      <c r="H84">
+        <v>12.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>4.69</v>
+      </c>
+      <c r="K84">
+        <v>2.17</v>
+      </c>
+      <c r="L84">
+        <v>2.52</v>
+      </c>
+      <c r="M84">
+        <v>12.7476216</v>
+      </c>
+      <c r="N84">
+        <v>-10.2276216</v>
+      </c>
+      <c r="O84">
+        <v>-2.454629184</v>
+      </c>
+      <c r="P84">
+        <v>-7.772992416000001</v>
+      </c>
+      <c r="Q84">
+        <v>-5.602992416000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>1.403173532298388</v>
+      </c>
+      <c r="T84">
+        <v>5.124203718358921</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04744414440416085</v>
+      </c>
+      <c r="W84">
+        <v>0.2274703383162864</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1976839350173368</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.4410969132330647</v>
+      </c>
+      <c r="C85">
+        <v>-5.704169883007282</v>
+      </c>
+      <c r="D85">
+        <v>48.11683011699272</v>
+      </c>
+      <c r="E85">
+        <v>1.733000000000004</v>
+      </c>
+      <c r="F85">
+        <v>54.033</v>
+      </c>
+      <c r="G85">
+        <v>0.212</v>
+      </c>
+      <c r="H85">
+        <v>12.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>4.69</v>
+      </c>
+      <c r="K85">
+        <v>2.17</v>
+      </c>
+      <c r="L85">
+        <v>2.52</v>
+      </c>
+      <c r="M85">
+        <v>12.9030804</v>
+      </c>
+      <c r="N85">
+        <v>-10.3830804</v>
+      </c>
+      <c r="O85">
+        <v>-2.491939296</v>
+      </c>
+      <c r="P85">
+        <v>-7.891141104000001</v>
+      </c>
+      <c r="Q85">
+        <v>-5.721141104000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.483430798904176</v>
+      </c>
+      <c r="T85">
+        <v>5.425627466497683</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.04687252820652035</v>
+      </c>
+      <c r="W85">
+        <v>0.227606840264283</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1953022008605014</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.4430969132330647</v>
+      </c>
+      <c r="C86">
+        <v>-6.593197078081374</v>
+      </c>
+      <c r="D86">
+        <v>47.87880292191861</v>
+      </c>
+      <c r="E86">
+        <v>2.383999999999993</v>
+      </c>
+      <c r="F86">
+        <v>54.68399999999999</v>
+      </c>
+      <c r="G86">
+        <v>0.212</v>
+      </c>
+      <c r="H86">
+        <v>12.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>4.69</v>
+      </c>
+      <c r="K86">
+        <v>2.17</v>
+      </c>
+      <c r="L86">
+        <v>2.52</v>
+      </c>
+      <c r="M86">
+        <v>13.0585392</v>
+      </c>
+      <c r="N86">
+        <v>-10.5385392</v>
+      </c>
+      <c r="O86">
+        <v>-2.529249408</v>
+      </c>
+      <c r="P86">
+        <v>-8.009289791999999</v>
+      </c>
+      <c r="Q86">
+        <v>-5.839289791999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.573720223835686</v>
+      </c>
+      <c r="T86">
+        <v>5.764729183153785</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0463145219183475</v>
+      </c>
+      <c r="W86">
+        <v>0.2277400921658986</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1929771746597813</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.4450969132330648</v>
+      </c>
+      <c r="C87">
+        <v>-7.479880891383971</v>
+      </c>
+      <c r="D87">
+        <v>47.64311910861602</v>
+      </c>
+      <c r="E87">
+        <v>3.034999999999997</v>
+      </c>
+      <c r="F87">
+        <v>55.33499999999999</v>
+      </c>
+      <c r="G87">
+        <v>0.212</v>
+      </c>
+      <c r="H87">
+        <v>12.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>4.69</v>
+      </c>
+      <c r="K87">
+        <v>2.17</v>
+      </c>
+      <c r="L87">
+        <v>2.52</v>
+      </c>
+      <c r="M87">
+        <v>13.213998</v>
+      </c>
+      <c r="N87">
+        <v>-10.693998</v>
+      </c>
+      <c r="O87">
+        <v>-2.56655952</v>
+      </c>
+      <c r="P87">
+        <v>-8.127438479999999</v>
+      </c>
+      <c r="Q87">
+        <v>-5.957438479999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.676048238758066</v>
+      </c>
+      <c r="T87">
+        <v>6.149044462030704</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04576964518989635</v>
+      </c>
+      <c r="W87">
+        <v>0.2278702087286528</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1907068549579014</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.4470969132330647</v>
+      </c>
+      <c r="C88">
+        <v>-8.364255759351288</v>
+      </c>
+      <c r="D88">
+        <v>47.40974424064871</v>
+      </c>
+      <c r="E88">
+        <v>3.686</v>
+      </c>
+      <c r="F88">
+        <v>55.986</v>
+      </c>
+      <c r="G88">
+        <v>0.212</v>
+      </c>
+      <c r="H88">
+        <v>12.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>4.69</v>
+      </c>
+      <c r="K88">
+        <v>2.17</v>
+      </c>
+      <c r="L88">
+        <v>2.52</v>
+      </c>
+      <c r="M88">
+        <v>13.3694568</v>
+      </c>
+      <c r="N88">
+        <v>-10.8494568</v>
+      </c>
+      <c r="O88">
+        <v>-2.603869632</v>
+      </c>
+      <c r="P88">
+        <v>-8.245587168</v>
+      </c>
+      <c r="Q88">
+        <v>-6.075587168</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.792994541526499</v>
+      </c>
+      <c r="T88">
+        <v>6.588261923604326</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.04523744001326965</v>
+      </c>
+      <c r="W88">
+        <v>0.2279972993248312</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1884893333886235</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.4490969132330647</v>
+      </c>
+      <c r="C89">
+        <v>-9.246355446975386</v>
+      </c>
+      <c r="D89">
+        <v>47.1786445530246</v>
+      </c>
+      <c r="E89">
+        <v>4.336999999999996</v>
+      </c>
+      <c r="F89">
+        <v>56.63699999999999</v>
+      </c>
+      <c r="G89">
+        <v>0.212</v>
+      </c>
+      <c r="H89">
+        <v>12.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>4.69</v>
+      </c>
+      <c r="K89">
+        <v>2.17</v>
+      </c>
+      <c r="L89">
+        <v>2.52</v>
+      </c>
+      <c r="M89">
+        <v>13.5249156</v>
+      </c>
+      <c r="N89">
+        <v>-11.0049156</v>
+      </c>
+      <c r="O89">
+        <v>-2.641179744</v>
+      </c>
+      <c r="P89">
+        <v>-8.363735856</v>
+      </c>
+      <c r="Q89">
+        <v>-6.193735856</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.927932583182383</v>
+      </c>
+      <c r="T89">
+        <v>7.095051302343119</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04471746943840448</v>
+      </c>
+      <c r="W89">
+        <v>0.228121468298109</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1863227893266853</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.4510969132330647</v>
+      </c>
+      <c r="C90">
+        <v>-10.12621306408957</v>
+      </c>
+      <c r="D90">
+        <v>46.94978693591042</v>
+      </c>
+      <c r="E90">
+        <v>4.988</v>
+      </c>
+      <c r="F90">
+        <v>57.288</v>
+      </c>
+      <c r="G90">
+        <v>0.212</v>
+      </c>
+      <c r="H90">
+        <v>12.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>4.69</v>
+      </c>
+      <c r="K90">
+        <v>2.17</v>
+      </c>
+      <c r="L90">
+        <v>2.52</v>
+      </c>
+      <c r="M90">
+        <v>13.6803744</v>
+      </c>
+      <c r="N90">
+        <v>-11.1603744</v>
+      </c>
+      <c r="O90">
+        <v>-2.678489856</v>
+      </c>
+      <c r="P90">
+        <v>-8.481884544</v>
+      </c>
+      <c r="Q90">
+        <v>-6.311884544</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>2.085360298447582</v>
+      </c>
+      <c r="T90">
+        <v>7.686305577538381</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04420931637660443</v>
+      </c>
+      <c r="W90">
+        <v>0.2282428152492669</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1842054849025184</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.4530969132330647</v>
+      </c>
+      <c r="C91">
+        <v>-11.00386108118208</v>
+      </c>
+      <c r="D91">
+        <v>46.72313891881791</v>
+      </c>
+      <c r="E91">
+        <v>5.638999999999996</v>
+      </c>
+      <c r="F91">
+        <v>57.93899999999999</v>
+      </c>
+      <c r="G91">
+        <v>0.212</v>
+      </c>
+      <c r="H91">
+        <v>12.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>4.69</v>
+      </c>
+      <c r="K91">
+        <v>2.17</v>
+      </c>
+      <c r="L91">
+        <v>2.52</v>
+      </c>
+      <c r="M91">
+        <v>13.8358332</v>
+      </c>
+      <c r="N91">
+        <v>-11.3158332</v>
+      </c>
+      <c r="O91">
+        <v>-2.715799968</v>
+      </c>
+      <c r="P91">
+        <v>-8.600033232000001</v>
+      </c>
+      <c r="Q91">
+        <v>-6.430033232000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>2.27141123467009</v>
+      </c>
+      <c r="T91">
+        <v>8.38506063004187</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04371258248473247</v>
+      </c>
+      <c r="W91">
+        <v>0.2283614353026459</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1821357603530519</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.4550969132330647</v>
+      </c>
+      <c r="C92">
+        <v>-11.87933134475409</v>
+      </c>
+      <c r="D92">
+        <v>46.49866865524591</v>
+      </c>
+      <c r="E92">
+        <v>6.289999999999999</v>
+      </c>
+      <c r="F92">
+        <v>58.59</v>
+      </c>
+      <c r="G92">
+        <v>0.212</v>
+      </c>
+      <c r="H92">
+        <v>12.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>4.69</v>
+      </c>
+      <c r="K92">
+        <v>2.17</v>
+      </c>
+      <c r="L92">
+        <v>2.52</v>
+      </c>
+      <c r="M92">
+        <v>13.991292</v>
+      </c>
+      <c r="N92">
+        <v>-11.471292</v>
+      </c>
+      <c r="O92">
+        <v>-2.75311008</v>
+      </c>
+      <c r="P92">
+        <v>-8.718181919999999</v>
+      </c>
+      <c r="Q92">
+        <v>-6.548181919999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>2.494672358137099</v>
+      </c>
+      <c r="T92">
+        <v>9.22356669304606</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.043226887123791</v>
+      </c>
+      <c r="W92">
+        <v>0.2284774193548387</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1801120296824624</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.4570969132330647</v>
+      </c>
+      <c r="C93">
+        <v>-12.75265509223695</v>
+      </c>
+      <c r="D93">
+        <v>46.27634490776305</v>
+      </c>
+      <c r="E93">
+        <v>6.941000000000003</v>
+      </c>
+      <c r="F93">
+        <v>59.241</v>
+      </c>
+      <c r="G93">
+        <v>0.212</v>
+      </c>
+      <c r="H93">
+        <v>12.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>4.69</v>
+      </c>
+      <c r="K93">
+        <v>2.17</v>
+      </c>
+      <c r="L93">
+        <v>2.52</v>
+      </c>
+      <c r="M93">
+        <v>14.1467508</v>
+      </c>
+      <c r="N93">
+        <v>-11.6267508</v>
+      </c>
+      <c r="O93">
+        <v>-2.790420192</v>
+      </c>
+      <c r="P93">
+        <v>-8.836330608000001</v>
+      </c>
+      <c r="Q93">
+        <v>-6.666330608000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>2.767547064596777</v>
+      </c>
+      <c r="T93">
+        <v>10.24840743671784</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04275186638616692</v>
+      </c>
+      <c r="W93">
+        <v>0.2285908543069834</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1781327766090288</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.4590969132330647</v>
+      </c>
+      <c r="C94">
+        <v>-13.6238629664837</v>
+      </c>
+      <c r="D94">
+        <v>46.05613703351629</v>
+      </c>
+      <c r="E94">
+        <v>7.591999999999999</v>
+      </c>
+      <c r="F94">
+        <v>59.892</v>
+      </c>
+      <c r="G94">
+        <v>0.212</v>
+      </c>
+      <c r="H94">
+        <v>12.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>4.69</v>
+      </c>
+      <c r="K94">
+        <v>2.17</v>
+      </c>
+      <c r="L94">
+        <v>2.52</v>
+      </c>
+      <c r="M94">
+        <v>14.3022096</v>
+      </c>
+      <c r="N94">
+        <v>-11.7822096</v>
+      </c>
+      <c r="O94">
+        <v>-2.827730304</v>
+      </c>
+      <c r="P94">
+        <v>-8.954479296000001</v>
+      </c>
+      <c r="Q94">
+        <v>-6.784479296000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>3.108640447671375</v>
+      </c>
+      <c r="T94">
+        <v>11.52945836630758</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04228717218631728</v>
+      </c>
+      <c r="W94">
+        <v>0.2287018232819074</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.176196550776322</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.4610969132330647</v>
+      </c>
+      <c r="C95">
+        <v>-14.49298502984863</v>
+      </c>
+      <c r="D95">
+        <v>45.83801497015136</v>
+      </c>
+      <c r="E95">
+        <v>8.243000000000002</v>
+      </c>
+      <c r="F95">
+        <v>60.543</v>
+      </c>
+      <c r="G95">
+        <v>0.212</v>
+      </c>
+      <c r="H95">
+        <v>12.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>4.69</v>
+      </c>
+      <c r="K95">
+        <v>2.17</v>
+      </c>
+      <c r="L95">
+        <v>2.52</v>
+      </c>
+      <c r="M95">
+        <v>14.4576684</v>
+      </c>
+      <c r="N95">
+        <v>-11.9376684</v>
+      </c>
+      <c r="O95">
+        <v>-2.865040416</v>
+      </c>
+      <c r="P95">
+        <v>-9.072627984</v>
+      </c>
+      <c r="Q95">
+        <v>-6.902627984</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>3.547189083053</v>
+      </c>
+      <c r="T95">
+        <v>13.17652384720866</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04183247141012032</v>
+      </c>
+      <c r="W95">
+        <v>0.2288104058272633</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1743019642088346</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.4630969132330646</v>
+      </c>
+      <c r="C96">
+        <v>-15.36005077786868</v>
+      </c>
+      <c r="D96">
+        <v>45.62194922213131</v>
+      </c>
+      <c r="E96">
+        <v>8.893999999999998</v>
+      </c>
+      <c r="F96">
+        <v>61.194</v>
+      </c>
+      <c r="G96">
+        <v>0.212</v>
+      </c>
+      <c r="H96">
+        <v>12.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>4.69</v>
+      </c>
+      <c r="K96">
+        <v>2.17</v>
+      </c>
+      <c r="L96">
+        <v>2.52</v>
+      </c>
+      <c r="M96">
+        <v>14.6131272</v>
+      </c>
+      <c r="N96">
+        <v>-12.0931272</v>
+      </c>
+      <c r="O96">
+        <v>-2.902350528</v>
+      </c>
+      <c r="P96">
+        <v>-9.190776672</v>
+      </c>
+      <c r="Q96">
+        <v>-7.020776672</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>4.131920596895167</v>
+      </c>
+      <c r="T96">
+        <v>15.37261115507677</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0413874451185233</v>
+      </c>
+      <c r="W96">
+        <v>0.2289166781056966</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.172447687993847</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.4650969132330647</v>
+      </c>
+      <c r="C97">
+        <v>-16.22508915255984</v>
+      </c>
+      <c r="D97">
+        <v>45.40791084744016</v>
+      </c>
+      <c r="E97">
+        <v>9.545000000000002</v>
+      </c>
+      <c r="F97">
+        <v>61.845</v>
+      </c>
+      <c r="G97">
+        <v>0.212</v>
+      </c>
+      <c r="H97">
+        <v>12.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>4.69</v>
+      </c>
+      <c r="K97">
+        <v>2.17</v>
+      </c>
+      <c r="L97">
+        <v>2.52</v>
+      </c>
+      <c r="M97">
+        <v>14.768586</v>
+      </c>
+      <c r="N97">
+        <v>-12.248586</v>
+      </c>
+      <c r="O97">
+        <v>-2.93966064</v>
+      </c>
+      <c r="P97">
+        <v>-9.308925360000002</v>
+      </c>
+      <c r="Q97">
+        <v>-7.138925360000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>4.950544716274203</v>
+      </c>
+      <c r="T97">
+        <v>18.44713338609214</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04095178780148621</v>
+      </c>
+      <c r="W97">
+        <v>0.2290207130730051</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1706324491728591</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.4670969132330647</v>
+      </c>
+      <c r="C98">
+        <v>-17.08812855534082</v>
+      </c>
+      <c r="D98">
+        <v>45.19587144465917</v>
+      </c>
+      <c r="E98">
+        <v>10.196</v>
+      </c>
+      <c r="F98">
+        <v>62.496</v>
+      </c>
+      <c r="G98">
+        <v>0.212</v>
+      </c>
+      <c r="H98">
+        <v>12.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>4.69</v>
+      </c>
+      <c r="K98">
+        <v>2.17</v>
+      </c>
+      <c r="L98">
+        <v>2.52</v>
+      </c>
+      <c r="M98">
+        <v>14.9240448</v>
+      </c>
+      <c r="N98">
+        <v>-12.4040448</v>
+      </c>
+      <c r="O98">
+        <v>-2.976970752</v>
+      </c>
+      <c r="P98">
+        <v>-9.427074048</v>
+      </c>
+      <c r="Q98">
+        <v>-7.257074048</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>6.178480895342741</v>
+      </c>
+      <c r="T98">
+        <v>23.05891673261512</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04052520667855406</v>
+      </c>
+      <c r="W98">
+        <v>0.2291225806451613</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1688550278273085</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.4690969132330647</v>
+      </c>
+      <c r="C99">
+        <v>-17.94919685959649</v>
+      </c>
+      <c r="D99">
+        <v>44.9858031404035</v>
+      </c>
+      <c r="E99">
+        <v>10.84699999999999</v>
+      </c>
+      <c r="F99">
+        <v>63.14699999999999</v>
+      </c>
+      <c r="G99">
+        <v>0.212</v>
+      </c>
+      <c r="H99">
+        <v>12.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>4.69</v>
+      </c>
+      <c r="K99">
+        <v>2.17</v>
+      </c>
+      <c r="L99">
+        <v>2.52</v>
+      </c>
+      <c r="M99">
+        <v>15.0795036</v>
+      </c>
+      <c r="N99">
+        <v>-12.5595036</v>
+      </c>
+      <c r="O99">
+        <v>-3.014280864</v>
+      </c>
+      <c r="P99">
+        <v>-9.545222735999999</v>
+      </c>
+      <c r="Q99">
+        <v>-7.375222736</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>8.22504119379032</v>
+      </c>
+      <c r="T99">
+        <v>30.74522231015349</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04010742104269268</v>
+      </c>
+      <c r="W99">
+        <v>0.229222347855005</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1671142543445528</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.4710969132330647</v>
+      </c>
+      <c r="C100">
+        <v>-18.80832142289243</v>
+      </c>
+      <c r="D100">
+        <v>44.77767857710757</v>
+      </c>
+      <c r="E100">
+        <v>11.498</v>
+      </c>
+      <c r="F100">
+        <v>63.79799999999999</v>
+      </c>
+      <c r="G100">
+        <v>0.212</v>
+      </c>
+      <c r="H100">
+        <v>12.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>4.69</v>
+      </c>
+      <c r="K100">
+        <v>2.17</v>
+      </c>
+      <c r="L100">
+        <v>2.52</v>
+      </c>
+      <c r="M100">
+        <v>15.2349624</v>
+      </c>
+      <c r="N100">
+        <v>-12.7149624</v>
+      </c>
+      <c r="O100">
+        <v>-3.051590976</v>
+      </c>
+      <c r="P100">
+        <v>-9.663371423999999</v>
+      </c>
+      <c r="Q100">
+        <v>-7.493371423999999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>12.31816179068548</v>
+      </c>
+      <c r="T100">
+        <v>46.11783346523025</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03969816164429785</v>
+      </c>
+      <c r="W100">
+        <v>0.2293200789993417</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.165409006851241</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.4730969132330647</v>
+      </c>
+      <c r="C101">
+        <v>-19.66552909885201</v>
+      </c>
+      <c r="D101">
+        <v>44.57147090114798</v>
+      </c>
+      <c r="E101">
+        <v>12.149</v>
+      </c>
+      <c r="F101">
+        <v>64.449</v>
+      </c>
+      <c r="G101">
+        <v>0.212</v>
+      </c>
+      <c r="H101">
+        <v>12.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>4.69</v>
+      </c>
+      <c r="K101">
+        <v>2.17</v>
+      </c>
+      <c r="L101">
+        <v>2.52</v>
+      </c>
+      <c r="M101">
+        <v>15.3904212</v>
+      </c>
+      <c r="N101">
+        <v>-12.8704212</v>
+      </c>
+      <c r="O101">
+        <v>-3.088901088</v>
+      </c>
+      <c r="P101">
+        <v>-9.781520112000001</v>
+      </c>
+      <c r="Q101">
+        <v>-7.611520112000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>24.59752358137096</v>
+      </c>
+      <c r="T101">
+        <v>92.23566693046048</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03929717011253727</v>
+      </c>
+      <c r="W101">
+        <v>0.2294158357771261</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1637382088022385</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
